--- a/IBC_prijamnik_VB/Project Outputs for IBC_prijamnik_VB/IBC_prijamnik_VB.xlsx
+++ b/IBC_prijamnik_VB/Project Outputs for IBC_prijamnik_VB/IBC_prijamnik_VB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FER\3. godina\6. sem\zavrsni\IBC_prijamnik_VB\Project Outputs for IBC_prijamnik_VB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{30966BE5-F030-463A-8668-56FD62CABD34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B870638-23EF-45B4-A8B6-CD251EEFA135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{5D130C20-71C6-4E3E-AA30-F23267941253}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{5EA72C9A-FCAD-4580-8617-08010BBABAA0}"/>
   </bookViews>
   <sheets>
     <sheet name="IBC_prijamnik_VB" sheetId="1" r:id="rId1"/>
@@ -34,12 +34,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="255">
   <si>
     <t>Komponenta</t>
   </si>
@@ -116,264 +119,264 @@
     <t>0805</t>
   </si>
   <si>
+    <t>KYOCERA AVX</t>
+  </si>
+  <si>
+    <t>08055C104ZAT2A</t>
+  </si>
+  <si>
+    <t>581-08055C104ZAT2A</t>
+  </si>
+  <si>
+    <t>100p</t>
+  </si>
+  <si>
+    <t>Multilayer Ceramic Capacitors MLCC - SMD/SMT 0805 450V 100pF C0G 5% T:0.6mm</t>
+  </si>
+  <si>
+    <t>C5</t>
+  </si>
+  <si>
+    <t>TDK</t>
+  </si>
+  <si>
+    <t>C2012C0G2W101J060AA</t>
+  </si>
+  <si>
+    <t>810-C2012C0G2W101JAA</t>
+  </si>
+  <si>
+    <t>680p</t>
+  </si>
+  <si>
+    <t>Multilayer Ceramic Capacitors MLCC - SMD/SMT 50V 680pF X7R 0402 1 0% AEC-Q200</t>
+  </si>
+  <si>
+    <t>C8</t>
+  </si>
+  <si>
+    <t>0402</t>
+  </si>
+  <si>
+    <t>KAM05AR71H681KN</t>
+  </si>
+  <si>
+    <t>581-KAM05AR71H681KN</t>
+  </si>
+  <si>
+    <t>15p</t>
+  </si>
+  <si>
+    <t>CAP CER 15PF 200V NP0 0805</t>
+  </si>
+  <si>
+    <t>C10, C11</t>
+  </si>
+  <si>
+    <t>08052U150JAT2A</t>
+  </si>
+  <si>
+    <t>581-08052U150J</t>
+  </si>
+  <si>
+    <t>Elektrolitski kondenzator</t>
+  </si>
+  <si>
+    <t>10u</t>
+  </si>
+  <si>
+    <t>Aluminum Electrolytic Capacitor, 10 uF, +/- 20%, -40 to 85 degC, 2-Pin SMD, RoHS, Tape and Reel</t>
+  </si>
+  <si>
+    <t>C12</t>
+  </si>
+  <si>
+    <t>Yageo Group</t>
+  </si>
+  <si>
+    <t>EEV106M035A9DAA</t>
+  </si>
+  <si>
+    <t>80-EEV106M035A9DAA</t>
+  </si>
+  <si>
+    <t>4u7</t>
+  </si>
+  <si>
+    <t>Cap Ceramic 4.7uF 50V X7R 10% Pad SMD 0805 125C T/R</t>
+  </si>
+  <si>
+    <t>C21, C22</t>
+  </si>
+  <si>
+    <t>CGA4J1X7R1H475K125AC</t>
+  </si>
+  <si>
+    <t>810-CGA4J1X7R1H475K1</t>
+  </si>
+  <si>
+    <t>1p2</t>
+  </si>
+  <si>
+    <t>JOHANSON TECHNOLOGY         500R07S1R2BV4T            MLCC CAPACITOR, 1.2PF, 50V, C0G/NP0, 0.1PF, 0402, FULL REEL</t>
+  </si>
+  <si>
+    <t>C23</t>
+  </si>
+  <si>
+    <t>QSCF500Q1R2B1GV001T</t>
+  </si>
+  <si>
+    <t>609-QSCF500Q1R2B1GV0</t>
+  </si>
+  <si>
+    <t>10n</t>
+  </si>
+  <si>
+    <t>KEMET - C0805C103K5RECAUTO - CAP, AEC-Q200, 0.01UF, 50V, MLCC, 0805</t>
+  </si>
+  <si>
+    <t>C25</t>
+  </si>
+  <si>
+    <t>C0805C103K5RECAUTO</t>
+  </si>
+  <si>
+    <t>80-C0805C103K5RECAUT</t>
+  </si>
+  <si>
+    <t>1u</t>
+  </si>
+  <si>
+    <t>Ceramic Capacitor, Multilayer, Ceramic, 50V, 10% +Tol, 10% -Tol, X7R, 15% TC, 1uF, Surface Mount, 0603</t>
+  </si>
+  <si>
+    <t>C27</t>
+  </si>
+  <si>
+    <t>0603</t>
+  </si>
+  <si>
+    <t>C1608X7R1H105K080AB</t>
+  </si>
+  <si>
+    <t>810-C1608X7R1H105K08</t>
+  </si>
+  <si>
+    <t>Keramicki konenzator</t>
+  </si>
+  <si>
+    <t>22p</t>
+  </si>
+  <si>
+    <t>Multilayer Ceramic Capacitors MLCC - SMD/SMT 50V 22pF C0G 0402 1% AEC-Q200</t>
+  </si>
+  <si>
+    <t>C28</t>
+  </si>
+  <si>
+    <t>KAM05ACG1H220FH</t>
+  </si>
+  <si>
+    <t>581-KAM05ACG1H220FH</t>
+  </si>
+  <si>
+    <t>Zelena dioda</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>Reel / LED, SMD, 0805, 2 Leads, Green, Water Clear Lens, 130 Deg Viewing Angle, Low Current</t>
+  </si>
+  <si>
+    <t>D1, D2</t>
+  </si>
+  <si>
+    <t>Bivar</t>
+  </si>
+  <si>
+    <t>SM0805GCL</t>
+  </si>
+  <si>
+    <t>749-SM0805GCL</t>
+  </si>
+  <si>
+    <t>Feritna perla</t>
+  </si>
+  <si>
+    <t>MPZ2012S601AT000</t>
+  </si>
+  <si>
+    <t>FERRITE BEAD 600 OHM 0805 1LN</t>
+  </si>
+  <si>
+    <t>FB1</t>
+  </si>
+  <si>
+    <t>810-MPZ2012S601AT000</t>
+  </si>
+  <si>
+    <t>IPD</t>
+  </si>
+  <si>
+    <t>MLPF-WB55-01E3</t>
+  </si>
+  <si>
+    <t>RF FILTER, 2.4GHZ TO 2.5GHZ, WLCSP-6;</t>
+  </si>
+  <si>
+    <t>IPD1</t>
+  </si>
+  <si>
+    <t>STMicroelectronics</t>
+  </si>
+  <si>
+    <t>511-MLPF-WB55-01E3</t>
+  </si>
+  <si>
+    <t>USB_C konektor</t>
+  </si>
+  <si>
+    <t>USB4135-GF-A</t>
+  </si>
+  <si>
+    <t>USB Connectors USBC Rec GF RA 6P SMT-SMT stakes 3.16mm</t>
+  </si>
+  <si>
+    <t>J1</t>
+  </si>
+  <si>
+    <t>Global Connector Technology</t>
+  </si>
+  <si>
+    <t>640-USB4135-GF-A</t>
+  </si>
+  <si>
+    <t>Header za bateriju?</t>
+  </si>
+  <si>
+    <t>BAT HEADER 2-1</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>J2</t>
+  </si>
+  <si>
+    <t>Zavojnica</t>
+  </si>
+  <si>
+    <t>Power Inductors - SMD 10 UH 20%</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
     <t>TAIYO YUDEN</t>
   </si>
   <si>
-    <t>MCJCU21GBB7104KTPA01</t>
-  </si>
-  <si>
-    <t>963-MCJCU21GBB7104KT</t>
-  </si>
-  <si>
-    <t>100p</t>
-  </si>
-  <si>
-    <t>Multilayer Ceramic Capacitors MLCC - SMD/SMT 0805 450V 100pF C0G 5% T:0.6mm</t>
-  </si>
-  <si>
-    <t>C5</t>
-  </si>
-  <si>
-    <t>TDK</t>
-  </si>
-  <si>
-    <t>C2012C0G2W101J060AA</t>
-  </si>
-  <si>
-    <t>810-C2012C0G2W101JAA</t>
-  </si>
-  <si>
-    <t>680p</t>
-  </si>
-  <si>
-    <t>Multilayer Ceramic Capacitors MLCC - SMD/SMT 50V 680pF X7R 0402 1 0% AEC-Q200</t>
-  </si>
-  <si>
-    <t>C8</t>
-  </si>
-  <si>
-    <t>0402</t>
-  </si>
-  <si>
-    <t>KYOCERA AVX</t>
-  </si>
-  <si>
-    <t>KAM05AR71H681KN</t>
-  </si>
-  <si>
-    <t>581-KAM05AR71H681KN</t>
-  </si>
-  <si>
-    <t>15p</t>
-  </si>
-  <si>
-    <t>CAP CER 15PF 200V NP0 0805</t>
-  </si>
-  <si>
-    <t>C10, C11</t>
-  </si>
-  <si>
-    <t>08052U150JAT2A</t>
-  </si>
-  <si>
-    <t>581-08052U150J</t>
-  </si>
-  <si>
-    <t>Elektrolitski kondenzator</t>
-  </si>
-  <si>
-    <t>10u</t>
-  </si>
-  <si>
-    <t>Aluminum Electrolytic Capacitor, 10 uF, +/- 20%, -40 to 85 degC, 2-Pin SMD, RoHS, Tape and Reel</t>
-  </si>
-  <si>
-    <t>C12</t>
-  </si>
-  <si>
-    <t>Yageo Group</t>
-  </si>
-  <si>
-    <t>EEV106M035A9DAA</t>
-  </si>
-  <si>
-    <t>80-EEV106M035A9DAA</t>
-  </si>
-  <si>
-    <t>4u7</t>
-  </si>
-  <si>
-    <t>Cap Ceramic 4.7uF 50V X7R 10% Pad SMD 0805 125C T/R</t>
-  </si>
-  <si>
-    <t>C21, C22</t>
-  </si>
-  <si>
-    <t>CGA4J1X7R1H475K125AC</t>
-  </si>
-  <si>
-    <t>810-CGA4J1X7R1H475K1</t>
-  </si>
-  <si>
-    <t>1p2</t>
-  </si>
-  <si>
-    <t>JOHANSON TECHNOLOGY         500R07S1R2BV4T            MLCC CAPACITOR, 1.2PF, 50V, C0G/NP0, 0.1PF, 0402, FULL REEL</t>
-  </si>
-  <si>
-    <t>C23</t>
-  </si>
-  <si>
-    <t>QSCF500Q1R2B1GV001T</t>
-  </si>
-  <si>
-    <t>609-QSCF500Q1R2B1GV0</t>
-  </si>
-  <si>
-    <t>10n</t>
-  </si>
-  <si>
-    <t>KEMET - C0805C103K5RECAUTO - CAP, AEC-Q200, 0.01UF, 50V, MLCC, 0805</t>
-  </si>
-  <si>
-    <t>C25</t>
-  </si>
-  <si>
-    <t>C0805C103K5RECAUTO</t>
-  </si>
-  <si>
-    <t>80-C0805C103K5RECAUT</t>
-  </si>
-  <si>
-    <t>1u</t>
-  </si>
-  <si>
-    <t>Ceramic Capacitor, Multilayer, Ceramic, 50V, 10% +Tol, 10% -Tol, X7R, 15% TC, 1uF, Surface Mount, 0603</t>
-  </si>
-  <si>
-    <t>C27</t>
-  </si>
-  <si>
-    <t>0603</t>
-  </si>
-  <si>
-    <t>C1608X7R1H105K080AB</t>
-  </si>
-  <si>
-    <t>810-C1608X7R1H105K08</t>
-  </si>
-  <si>
-    <t>Keramicki konenzator</t>
-  </si>
-  <si>
-    <t>22p</t>
-  </si>
-  <si>
-    <t>Multilayer Ceramic Capacitors MLCC - SMD/SMT 50V 22pF C0G 0402 1% AEC-Q200</t>
-  </si>
-  <si>
-    <t>C28</t>
-  </si>
-  <si>
-    <t>KAM05ACG1H220FH</t>
-  </si>
-  <si>
-    <t>581-KAM05ACG1H220FH</t>
-  </si>
-  <si>
-    <t>Zelena dioda</t>
-  </si>
-  <si>
-    <t>Green</t>
-  </si>
-  <si>
-    <t>Reel / LED, SMD, 0805, 2 Leads, Green, Water Clear Lens, 130 Deg Viewing Angle, Low Current</t>
-  </si>
-  <si>
-    <t>D1, D2</t>
-  </si>
-  <si>
-    <t>Bivar</t>
-  </si>
-  <si>
-    <t>SM0805GCL</t>
-  </si>
-  <si>
-    <t>749-SM0805GCL</t>
-  </si>
-  <si>
-    <t>Feritna perla</t>
-  </si>
-  <si>
-    <t>MPZ2012S601AT000</t>
-  </si>
-  <si>
-    <t>FERRITE BEAD 600 OHM 0805 1LN</t>
-  </si>
-  <si>
-    <t>FB1</t>
-  </si>
-  <si>
-    <t>810-MPZ2012S601AT000</t>
-  </si>
-  <si>
-    <t>IPD</t>
-  </si>
-  <si>
-    <t>MLPF-WB55-01E3</t>
-  </si>
-  <si>
-    <t>RF FILTER, 2.4GHZ TO 2.5GHZ, WLCSP-6;</t>
-  </si>
-  <si>
-    <t>IPD1</t>
-  </si>
-  <si>
-    <t>STMicroelectronics</t>
-  </si>
-  <si>
-    <t>511-MLPF-WB55-01E3</t>
-  </si>
-  <si>
-    <t>USB_C konektor</t>
-  </si>
-  <si>
-    <t>USB4135-GF-A</t>
-  </si>
-  <si>
-    <t>USB Connectors USBC Rec GF RA 6P SMT-SMT stakes 3.16mm</t>
-  </si>
-  <si>
-    <t>J1</t>
-  </si>
-  <si>
-    <t>Global Connector Technology</t>
-  </si>
-  <si>
-    <t>640-USB4135-GF-A</t>
-  </si>
-  <si>
-    <t>Header za bateriju?</t>
-  </si>
-  <si>
-    <t>BAT HEADER 2-1</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>J2</t>
-  </si>
-  <si>
-    <t>Zavojnica</t>
-  </si>
-  <si>
-    <t>Power Inductors - SMD 10 UH 20%</t>
-  </si>
-  <si>
-    <t>L1</t>
-  </si>
-  <si>
     <t>LSQBA201212T100KR</t>
   </si>
   <si>
@@ -557,9 +560,6 @@
     <t>R13</t>
   </si>
   <si>
-    <t>1206</t>
-  </si>
-  <si>
     <t>MCU08050C1501FP500</t>
   </si>
   <si>
@@ -587,7 +587,7 @@
     <t>Ferrite Beads BMC-Q 0402 ZR 0-15R Tol. UH Current</t>
   </si>
   <si>
-    <t>R16, R17, R18</t>
+    <t>R16</t>
   </si>
   <si>
     <t>TE Connectivity / Sigma</t>
@@ -597,6 +597,9 @@
   </si>
   <si>
     <t>279-BMC-Q1E0000M</t>
+  </si>
+  <si>
+    <t>R17, R18</t>
   </si>
   <si>
     <t>Sklopka</t>
@@ -1199,8 +1202,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FA801F3-CE0E-4321-B313-BEE789F521D8}">
-  <dimension ref="A1:L43"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A0F86D1-A5F9-42C4-9426-6EEF649C0F2E}">
+  <dimension ref="A1:L44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1283,13 +1286,13 @@
         <v>19</v>
       </c>
       <c r="J2" s="1">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="K2" s="1">
         <v>1</v>
       </c>
       <c r="L2" s="1">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -1321,13 +1324,13 @@
         <v>27</v>
       </c>
       <c r="J3" s="1">
-        <v>0.12472999999999999</v>
+        <v>0.13491</v>
       </c>
       <c r="K3" s="1">
         <v>17</v>
       </c>
       <c r="L3" s="1">
-        <v>2.12</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -1359,13 +1362,13 @@
         <v>33</v>
       </c>
       <c r="J4" s="1">
-        <v>0.15590999999999999</v>
+        <v>0.15368999999999999</v>
       </c>
       <c r="K4" s="1">
         <v>1</v>
       </c>
       <c r="L4" s="1">
-        <v>0.15590999999999999</v>
+        <v>0.15368999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -1385,25 +1388,25 @@
         <v>37</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="J5" s="1">
-        <v>0.30315999999999999</v>
+        <v>0.29885</v>
       </c>
       <c r="K5" s="1">
         <v>1</v>
       </c>
       <c r="L5" s="1">
-        <v>0.30315999999999999</v>
+        <v>0.29885</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -1411,73 +1414,73 @@
         <v>20</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>24</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="G6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="J6" s="1">
-        <v>0.26851999999999998</v>
+        <v>0.26468999999999998</v>
       </c>
       <c r="K6" s="1">
         <v>2</v>
       </c>
       <c r="L6" s="1">
-        <v>0.53703000000000001</v>
+        <v>0.52939000000000003</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="J7" s="1">
-        <v>0.28583999999999998</v>
+        <v>0.27322999999999997</v>
       </c>
       <c r="K7" s="1">
         <v>1</v>
       </c>
       <c r="L7" s="1">
-        <v>0.28583999999999998</v>
+        <v>0.27322999999999997</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -1485,13 +1488,13 @@
         <v>20</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>24</v>
@@ -1500,22 +1503,22 @@
         <v>31</v>
       </c>
       <c r="G8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="J8" s="1">
-        <v>0.46773999999999999</v>
+        <v>0.46107999999999999</v>
       </c>
       <c r="K8" s="1">
         <v>2</v>
       </c>
       <c r="L8" s="1">
-        <v>0.93547999999999998</v>
+        <v>0.92215999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -1523,13 +1526,13 @@
         <v>20</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>37</v>
@@ -1538,22 +1541,22 @@
         <v>17</v>
       </c>
       <c r="G9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="J9" s="1">
-        <v>0.13858999999999999</v>
+        <v>0.13661999999999999</v>
       </c>
       <c r="K9" s="1">
         <v>1</v>
       </c>
       <c r="L9" s="1">
-        <v>0.13858999999999999</v>
+        <v>0.13661999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -1561,37 +1564,37 @@
         <v>20</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>24</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="J10" s="1">
-        <v>0.20788000000000001</v>
+        <v>0.21346000000000001</v>
       </c>
       <c r="K10" s="1">
         <v>1</v>
       </c>
       <c r="L10" s="1">
-        <v>0.20788000000000001</v>
+        <v>0.21346000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -1599,127 +1602,127 @@
         <v>20</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>31</v>
       </c>
       <c r="G11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="J11" s="1">
-        <v>0.18190000000000001</v>
+        <v>0.17931</v>
       </c>
       <c r="K11" s="1">
         <v>1</v>
       </c>
       <c r="L11" s="1">
-        <v>0.18190000000000001</v>
+        <v>0.17931</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>37</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="G12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="J12" s="1">
-        <v>0.27717999999999998</v>
+        <v>0.27322999999999997</v>
       </c>
       <c r="K12" s="1">
         <v>1</v>
       </c>
       <c r="L12" s="1">
-        <v>0.27717999999999998</v>
+        <v>0.27322999999999997</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>83</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>24</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="H13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="J13" s="1">
-        <v>0.48505999999999999</v>
+        <v>0.47815999999999997</v>
       </c>
       <c r="K13" s="1">
         <v>2</v>
       </c>
       <c r="L13" s="1">
-        <v>0.97011999999999998</v>
+        <v>0.95630999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>24</v>
@@ -1728,108 +1731,108 @@
         <v>31</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J14" s="1">
-        <v>8.6620000000000003E-2</v>
+        <v>9.3920000000000003E-2</v>
       </c>
       <c r="K14" s="1">
         <v>1</v>
       </c>
       <c r="L14" s="1">
-        <v>8.6620000000000003E-2</v>
+        <v>9.3920000000000003E-2</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="J15" s="1">
-        <v>0.32049</v>
+        <v>0.31591999999999998</v>
       </c>
       <c r="K15" s="1">
         <v>1</v>
       </c>
       <c r="L15" s="1">
-        <v>0.32049</v>
+        <v>0.31591999999999998</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="J16" s="1">
-        <v>0.68428</v>
+        <v>0.58062000000000002</v>
       </c>
       <c r="K16" s="1">
         <v>1</v>
       </c>
       <c r="L16" s="1">
-        <v>0.68428</v>
+        <v>0.58062000000000002</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
@@ -1844,22 +1847,22 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>24</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>111</v>
@@ -1871,21 +1874,21 @@
         <v>112</v>
       </c>
       <c r="J18" s="1">
-        <v>9.5280000000000004E-2</v>
+        <v>9.3920000000000003E-2</v>
       </c>
       <c r="K18" s="1">
         <v>1</v>
       </c>
       <c r="L18" s="1">
-        <v>9.5280000000000004E-2</v>
+        <v>9.3920000000000003E-2</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>113</v>
@@ -1909,18 +1912,18 @@
         <v>117</v>
       </c>
       <c r="J19" s="1">
-        <v>0.10394</v>
+        <v>0.10246</v>
       </c>
       <c r="K19" s="1">
         <v>1</v>
       </c>
       <c r="L19" s="1">
-        <v>0.10394</v>
+        <v>0.10246</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>118</v>
@@ -1935,7 +1938,7 @@
         <v>37</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>121</v>
@@ -1947,18 +1950,18 @@
         <v>122</v>
       </c>
       <c r="J20" s="1">
-        <v>8.6620000000000003E-2</v>
+        <v>8.5389999999999994E-2</v>
       </c>
       <c r="K20" s="1">
         <v>1</v>
       </c>
       <c r="L20" s="1">
-        <v>8.6620000000000003E-2</v>
+        <v>8.5389999999999994E-2</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>123</v>
@@ -1985,13 +1988,13 @@
         <v>127</v>
       </c>
       <c r="J21" s="1">
-        <v>8.6620000000000003E-2</v>
+        <v>8.5389999999999994E-2</v>
       </c>
       <c r="K21" s="1">
         <v>1</v>
       </c>
       <c r="L21" s="1">
-        <v>8.6620000000000003E-2</v>
+        <v>8.5389999999999994E-2</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -2011,7 +2014,7 @@
         <v>24</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>132</v>
@@ -2023,13 +2026,13 @@
         <v>133</v>
       </c>
       <c r="J22" s="1">
-        <v>8.6599999999999993E-3</v>
+        <v>1.025E-2</v>
       </c>
       <c r="K22" s="1">
         <v>4</v>
       </c>
       <c r="L22" s="1">
-        <v>8.6620000000000003E-2</v>
+        <v>0.10246</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -2049,7 +2052,7 @@
         <v>24</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>137</v>
@@ -2061,13 +2064,13 @@
         <v>138</v>
       </c>
       <c r="J23" s="1">
-        <v>6.0600000000000003E-3</v>
+        <v>5.9800000000000001E-3</v>
       </c>
       <c r="K23" s="1">
         <v>2</v>
       </c>
       <c r="L23" s="1">
-        <v>6.0630000000000003E-2</v>
+        <v>5.9769999999999997E-2</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -2087,7 +2090,7 @@
         <v>24</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>142</v>
@@ -2099,13 +2102,13 @@
         <v>143</v>
       </c>
       <c r="J24" s="1">
-        <v>8.6620000000000003E-2</v>
+        <v>9.3920000000000003E-2</v>
       </c>
       <c r="K24" s="1">
         <v>1</v>
       </c>
       <c r="L24" s="1">
-        <v>8.6620000000000003E-2</v>
+        <v>9.3920000000000003E-2</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
@@ -2125,7 +2128,7 @@
         <v>24</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>147</v>
@@ -2137,13 +2140,13 @@
         <v>148</v>
       </c>
       <c r="J25" s="1">
-        <v>8.6620000000000003E-2</v>
+        <v>8.5389999999999994E-2</v>
       </c>
       <c r="K25" s="1">
         <v>1</v>
       </c>
       <c r="L25" s="1">
-        <v>8.6620000000000003E-2</v>
+        <v>8.5389999999999994E-2</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -2163,7 +2166,7 @@
         <v>24</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>152</v>
@@ -2175,13 +2178,13 @@
         <v>153</v>
       </c>
       <c r="J26" s="1">
-        <v>8.6620000000000003E-2</v>
+        <v>8.5389999999999994E-2</v>
       </c>
       <c r="K26" s="1">
         <v>1</v>
       </c>
       <c r="L26" s="1">
-        <v>8.6620000000000003E-2</v>
+        <v>8.5389999999999994E-2</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -2201,7 +2204,7 @@
         <v>24</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>157</v>
@@ -2213,13 +2216,13 @@
         <v>158</v>
       </c>
       <c r="J27" s="1">
-        <v>8.6620000000000003E-2</v>
+        <v>8.5389999999999994E-2</v>
       </c>
       <c r="K27" s="1">
         <v>1</v>
       </c>
       <c r="L27" s="1">
-        <v>8.6620000000000003E-2</v>
+        <v>8.5389999999999994E-2</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -2251,13 +2254,13 @@
         <v>162</v>
       </c>
       <c r="J28" s="1">
-        <v>9.5280000000000004E-2</v>
+        <v>9.3920000000000003E-2</v>
       </c>
       <c r="K28" s="1">
         <v>1</v>
       </c>
       <c r="L28" s="1">
-        <v>9.5280000000000004E-2</v>
+        <v>9.3920000000000003E-2</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
@@ -2274,7 +2277,7 @@
         <v>165</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>166</v>
@@ -2289,13 +2292,13 @@
         <v>168</v>
       </c>
       <c r="J29" s="1">
-        <v>0.13858999999999999</v>
+        <v>0.13661999999999999</v>
       </c>
       <c r="K29" s="1">
         <v>2</v>
       </c>
       <c r="L29" s="1">
-        <v>0.27717999999999998</v>
+        <v>0.27322999999999997</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -2312,28 +2315,28 @@
         <v>171</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>172</v>
+        <v>24</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>166</v>
       </c>
       <c r="G30" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="H30" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>174</v>
-      </c>
       <c r="J30" s="1">
-        <v>8.6620000000000003E-2</v>
+        <v>8.5389999999999994E-2</v>
       </c>
       <c r="K30" s="1">
         <v>1</v>
       </c>
       <c r="L30" s="1">
-        <v>8.6620000000000003E-2</v>
+        <v>8.5389999999999994E-2</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -2341,13 +2344,13 @@
         <v>128</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>24</v>
@@ -2356,22 +2359,22 @@
         <v>166</v>
       </c>
       <c r="G31" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="H31" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="J31" s="1">
-        <v>8.6620000000000003E-2</v>
+        <v>8.5389999999999994E-2</v>
       </c>
       <c r="K31" s="1">
         <v>1</v>
       </c>
       <c r="L31" s="1">
-        <v>8.6620000000000003E-2</v>
+        <v>8.5389999999999994E-2</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -2379,407 +2382,403 @@
         <v>128</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>37</v>
       </c>
       <c r="F32" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="H32" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I32" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="H32" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>185</v>
-      </c>
       <c r="J32" s="1">
-        <v>0.13858999999999999</v>
+        <v>0.13661999999999999</v>
       </c>
       <c r="K32" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L32" s="1">
-        <v>0.41576999999999997</v>
+        <v>0.27322999999999997</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>186</v>
+        <v>128</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E33" s="1"/>
+        <v>185</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="F33" s="2" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="J33" s="1">
-        <v>0.32915</v>
+        <v>0.13661999999999999</v>
       </c>
       <c r="K33" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L33" s="1">
-        <v>0.32915</v>
+        <v>0.27322999999999997</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E34" s="1"/>
       <c r="F34" s="2" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="J34" s="1">
-        <v>5.86</v>
+        <v>0.29885</v>
       </c>
       <c r="K34" s="1">
         <v>1</v>
       </c>
       <c r="L34" s="1">
-        <v>5.86</v>
+        <v>0.29885</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>203</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="E35" s="1"/>
       <c r="F35" s="2" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="J35" s="1">
-        <v>12.18</v>
+        <v>5.78</v>
       </c>
       <c r="K35" s="1">
         <v>1</v>
       </c>
       <c r="L35" s="1">
-        <v>12.18</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>96</v>
+        <v>204</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="J36" s="1">
-        <v>5.48</v>
+        <v>12.01</v>
       </c>
       <c r="K36" s="1">
         <v>1</v>
       </c>
       <c r="L36" s="1">
-        <v>5.48</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="E37" s="1"/>
+        <v>209</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>210</v>
+      </c>
       <c r="F37" s="2" t="s">
-        <v>196</v>
+        <v>95</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="J37" s="1">
-        <v>0.79688999999999999</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="J37" s="1"/>
       <c r="K37" s="1">
         <v>1</v>
       </c>
-      <c r="L37" s="1">
-        <v>0.79688999999999999</v>
-      </c>
+      <c r="L37" s="1"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>221</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="E38" s="1"/>
       <c r="F38" s="2" t="s">
         <v>196</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="J38" s="1">
-        <v>2.11</v>
+        <v>0.78554000000000002</v>
       </c>
       <c r="K38" s="1">
         <v>1</v>
       </c>
       <c r="L38" s="1">
-        <v>2.11</v>
+        <v>0.78554000000000002</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>24</v>
+        <v>221</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>227</v>
+        <v>196</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="J39" s="1">
-        <v>0.11260000000000001</v>
+        <v>2.08</v>
       </c>
       <c r="K39" s="1">
         <v>1</v>
       </c>
       <c r="L39" s="1">
-        <v>0.11260000000000001</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="E40" s="1"/>
+        <v>226</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="F40" s="2" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="J40" s="1">
-        <v>4.99</v>
+        <v>0.111</v>
       </c>
       <c r="K40" s="1">
         <v>1</v>
       </c>
       <c r="L40" s="1">
-        <v>4.99</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="2" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="J41" s="1">
-        <v>0.34647</v>
+        <v>4.92</v>
       </c>
       <c r="K41" s="1">
         <v>1</v>
       </c>
       <c r="L41" s="1">
-        <v>0.34647</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>24</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="E42" s="1"/>
       <c r="F42" s="2" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="J42" s="1">
-        <v>0.50239</v>
+        <v>0.34154000000000001</v>
       </c>
       <c r="K42" s="1">
         <v>1</v>
       </c>
       <c r="L42" s="1">
-        <v>0.50239</v>
+        <v>0.34154000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
@@ -2787,37 +2786,75 @@
         <v>242</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>252</v>
+        <v>24</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>246</v>
       </c>
       <c r="G43" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="J43" s="1">
+        <v>0.49523</v>
+      </c>
+      <c r="K43" s="1">
+        <v>1</v>
+      </c>
+      <c r="L43" s="1">
+        <v>0.49523</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="G44" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="H43" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I43" s="2" t="s">
+      <c r="H44" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I44" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="J43" s="1">
-        <v>0.73626000000000003</v>
-      </c>
-      <c r="K43" s="1">
-        <v>1</v>
-      </c>
-      <c r="L43" s="1">
-        <v>0.73626000000000003</v>
+      <c r="J44" s="1">
+        <v>0.72577000000000003</v>
+      </c>
+      <c r="K44" s="1">
+        <v>1</v>
+      </c>
+      <c r="L44" s="1">
+        <v>0.72577000000000003</v>
       </c>
     </row>
   </sheetData>

--- a/IBC_prijamnik_VB/Project Outputs for IBC_prijamnik_VB/IBC_prijamnik_VB.xlsx
+++ b/IBC_prijamnik_VB/Project Outputs for IBC_prijamnik_VB/IBC_prijamnik_VB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FER\3. godina\6. sem\zavrsni\IBC_prijamnik_VB\Project Outputs for IBC_prijamnik_VB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B870638-23EF-45B4-A8B6-CD251EEFA135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E4955A24-90D0-452F-AB9C-10150E67F73B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{5EA72C9A-FCAD-4580-8617-08010BBABAA0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{E6AD122A-DD58-4BF7-9983-D2D151E5CF72}"/>
   </bookViews>
   <sheets>
     <sheet name="IBC_prijamnik_VB" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="249">
   <si>
     <t>Komponenta</t>
   </si>
@@ -50,15 +50,15 @@
     <t>Vrijednost</t>
   </si>
   <si>
+    <t>Oznaka komponente</t>
+  </si>
+  <si>
+    <t>Kucište</t>
+  </si>
+  <si>
     <t>Opis</t>
   </si>
   <si>
-    <t>Designator</t>
-  </si>
-  <si>
-    <t>Kucište</t>
-  </si>
-  <si>
     <t>Proizvodac</t>
   </si>
   <si>
@@ -80,99 +80,426 @@
     <t>Ukupna cijena</t>
   </si>
   <si>
+    <t>USB port</t>
+  </si>
+  <si>
+    <t>USB4135-GF-A</t>
+  </si>
+  <si>
+    <t>J1</t>
+  </si>
+  <si>
+    <t>SMD-¸10, 11,14x6,78mm</t>
+  </si>
+  <si>
+    <t>USB Connectors USBC Rec GF RA 6P SMT-SMT stakes 3.16mm</t>
+  </si>
+  <si>
+    <t>Global Connector Technology</t>
+  </si>
+  <si>
+    <t>Mouser</t>
+  </si>
+  <si>
+    <t>640-USB4135-GF-A</t>
+  </si>
+  <si>
+    <t>LDO regulator</t>
+  </si>
+  <si>
+    <t>TPS73633DBVR</t>
+  </si>
+  <si>
+    <t>U5</t>
+  </si>
+  <si>
+    <t>SOT-23</t>
+  </si>
+  <si>
+    <t>IC REG LINEAR 3.3V 400MA SOT23-5</t>
+  </si>
+  <si>
+    <t>Texas Instruments</t>
+  </si>
+  <si>
+    <t>595-TPS73633DBVR</t>
+  </si>
+  <si>
+    <t>Sklopka</t>
+  </si>
+  <si>
+    <t>TL3301AF160QG</t>
+  </si>
+  <si>
+    <t>S1</t>
+  </si>
+  <si>
+    <t>SMD-4, 6x6mm</t>
+  </si>
+  <si>
+    <t>Tactile Switches 6mm SMT Gull Wing 5mm Act Height</t>
+  </si>
+  <si>
+    <t>E-Switch</t>
+  </si>
+  <si>
+    <t>612-TL3301AF1</t>
+  </si>
+  <si>
+    <t>Mikrokontroler</t>
+  </si>
+  <si>
+    <t>STM32WB55CGU6</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>UFQFPN-48</t>
+  </si>
+  <si>
+    <t>MCU 32-Bit STM32WB55 ARM Cortex M4 RISC 1MB Flash 1.7V to 3.6V 48-Pin UFQFPN Tray</t>
+  </si>
+  <si>
+    <t>STMicroelectronics</t>
+  </si>
+  <si>
+    <t>511-STM32WB55CGU6</t>
+  </si>
+  <si>
+    <t>Kristalni oscilator</t>
+  </si>
+  <si>
+    <t>NX2016SA-32MHz</t>
+  </si>
+  <si>
+    <t>Y1</t>
+  </si>
+  <si>
+    <t>0805</t>
+  </si>
+  <si>
+    <t>Crystal 32MHZ 6PF SMD</t>
+  </si>
+  <si>
+    <t>NDK</t>
+  </si>
+  <si>
+    <t>NX2016SA-32M-EXS00A-CS06465</t>
+  </si>
+  <si>
+    <t>DigiKey</t>
+  </si>
+  <si>
+    <t>644-1375-1-ND</t>
+  </si>
+  <si>
+    <t>NX2012SA-32.768kHz</t>
+  </si>
+  <si>
+    <t>Y2</t>
+  </si>
+  <si>
+    <t>Crystals CRYSTAL 32.768KHZ 12.5PF SMD</t>
+  </si>
+  <si>
+    <t>NX2012SA-32.768K-STD-MUB-1</t>
+  </si>
+  <si>
+    <t>344-NX2012SA32768K1</t>
+  </si>
+  <si>
+    <t>Feritna perla</t>
+  </si>
+  <si>
+    <t>MPZ2012S601AT000</t>
+  </si>
+  <si>
+    <t>FB1</t>
+  </si>
+  <si>
+    <t>FERRITE BEAD 600 OHM 0805 1LN</t>
+  </si>
+  <si>
+    <t>TDK</t>
+  </si>
+  <si>
+    <t>810-MPZ2012S601AT000</t>
+  </si>
+  <si>
+    <t>IPD RF Filter</t>
+  </si>
+  <si>
+    <t>MLPF-WB55-01E3</t>
+  </si>
+  <si>
+    <t>IPD1</t>
+  </si>
+  <si>
+    <t>SMD-6, 1,6x1 mm</t>
+  </si>
+  <si>
+    <t>RF FILTER, 2.4GHZ TO 2.5GHZ, WLCSP-6;</t>
+  </si>
+  <si>
+    <t>511-MLPF-WB55-01E3</t>
+  </si>
+  <si>
+    <t>Konektor</t>
+  </si>
+  <si>
+    <t>HDR 1X4</t>
+  </si>
+  <si>
+    <t>X2</t>
+  </si>
+  <si>
+    <t>10,16x2,5mm</t>
+  </si>
+  <si>
+    <t>CONN HEADER VERT 4POS 2.54MM</t>
+  </si>
+  <si>
+    <t>Adam Tech</t>
+  </si>
+  <si>
+    <t>PH1-12-UA</t>
+  </si>
+  <si>
+    <t>737-PH1-12-UA</t>
+  </si>
+  <si>
+    <t>Svjetleća dioda</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>D1, D2, D3</t>
+  </si>
+  <si>
+    <t>Reel / LED, SMD, 0805, 2 Leads, Green, Water Clear Lens, 130 Deg Viewing Angle, Low Current</t>
+  </si>
+  <si>
+    <t>Osram</t>
+  </si>
+  <si>
+    <t>Q65110A2395</t>
+  </si>
+  <si>
+    <t>720-Q65110A2395</t>
+  </si>
+  <si>
+    <t>Buffer</t>
+  </si>
+  <si>
+    <t>BUF602</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>High Speed Operational Amplifiers High Speed Closed Loop Buffer</t>
+  </si>
+  <si>
+    <t>BUF602ID</t>
+  </si>
+  <si>
+    <t>595-BUF602ID</t>
+  </si>
+  <si>
+    <t>Punjač za bateriju</t>
+  </si>
+  <si>
+    <t>BQ24040DSQR</t>
+  </si>
+  <si>
+    <t>U4</t>
+  </si>
+  <si>
+    <t>WSON-10</t>
+  </si>
+  <si>
+    <t>Battery Management 800mA Sng-Inpt Sg Cl Li-Ion Batt Charger A 595-BQ24040DSQT</t>
+  </si>
+  <si>
+    <t>595-BQ24040DSQR</t>
+  </si>
+  <si>
+    <t>Logaritamsko pojačalo</t>
+  </si>
+  <si>
+    <t>AD8310</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>MSOP-8</t>
+  </si>
+  <si>
+    <t>SP Amp LOG Amp Single R-R I/P 5.5V 8-Pin MSOP T/R</t>
+  </si>
+  <si>
+    <t>Analog Devices</t>
+  </si>
+  <si>
+    <t>AD8310ARMZ-REEL7</t>
+  </si>
+  <si>
+    <t>584-AD8310ARMZ-R7</t>
+  </si>
+  <si>
     <t>Antena</t>
   </si>
   <si>
     <t>2450AT18B100E</t>
   </si>
   <si>
+    <t>ANT1</t>
+  </si>
+  <si>
+    <t>CSMD</t>
+  </si>
+  <si>
     <t>JOHANSON TECHNOLOGY - 2450AT18B100E - ANTENNA, CERAMIC, 2.45GHZ</t>
   </si>
   <si>
-    <t>ANT1</t>
-  </si>
-  <si>
-    <t>CSMD</t>
-  </si>
-  <si>
     <t>Knowles</t>
   </si>
   <si>
-    <t>Mouser</t>
-  </si>
-  <si>
     <t>609-2450AT18B100E</t>
   </si>
   <si>
     <t>Keramicki kondenzator</t>
   </si>
   <si>
+    <t>100p</t>
+  </si>
+  <si>
+    <t>C20</t>
+  </si>
+  <si>
+    <t>0402</t>
+  </si>
+  <si>
+    <t>Multilayer Ceramic Capacitors MLCC - SMD/SMT 0402 100VDC 100pF 2% C0G AEC-Q200</t>
+  </si>
+  <si>
+    <t>Murata</t>
+  </si>
+  <si>
+    <t>GCM1555C2A101GE02D</t>
+  </si>
+  <si>
+    <t>81-GCM1555C2A101GE2D</t>
+  </si>
+  <si>
     <t>100n</t>
   </si>
   <si>
-    <t>CAP CER 0.1UF 50V X7R 0805</t>
-  </si>
-  <si>
-    <t>C1, C2, C3, C4, C6, C7, C9, C13, C14, C15, C16, C17, C18, C19, C20, C24, C26</t>
-  </si>
-  <si>
-    <t>0805</t>
+    <t>C1, C2, C3, C4, C6, C7, C9, C13, C14, C15, C16, C17, C19, C21, C24, C29, C30</t>
+  </si>
+  <si>
+    <t>Multilayer Ceramic Capacitors MLCC - SMD/SMT 50V 0.1uF X7R 0805 10% AEC-Q200</t>
+  </si>
+  <si>
+    <t>TAIYO YUDEN</t>
+  </si>
+  <si>
+    <t>MCJCU21GBB7104KTPA01</t>
+  </si>
+  <si>
+    <t>963-MCJCU21GBB7104KT</t>
+  </si>
+  <si>
+    <t>Schmittov trigger</t>
+  </si>
+  <si>
+    <t>74AHC1G17GWH</t>
+  </si>
+  <si>
+    <t>U6</t>
+  </si>
+  <si>
+    <t>Buffers &amp; Line Drivers SOT353-1 SNGL TRIGGER BUFFER</t>
+  </si>
+  <si>
+    <t>Nexperia</t>
+  </si>
+  <si>
+    <t>771-74AHC1G17GWH</t>
+  </si>
+  <si>
+    <t>Otpornik</t>
+  </si>
+  <si>
+    <t>52R3</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>RC0805FR-0752R3L 52,3Ohm</t>
+  </si>
+  <si>
+    <t>Yageo Group</t>
+  </si>
+  <si>
+    <t>RC0805FR-0752R3L</t>
+  </si>
+  <si>
+    <t>603-RC0805FR-0752R3L</t>
+  </si>
+  <si>
+    <t>49R9</t>
+  </si>
+  <si>
+    <t>R1, R3</t>
+  </si>
+  <si>
+    <t>Res Thick Film 0805 49.9 Ohm 1% 0.125W(1/8W) ±100ppm/C Epoxy Pad SMD Automotive T/R</t>
+  </si>
+  <si>
+    <t>AC0805FR-0749R9L</t>
+  </si>
+  <si>
+    <t>603-AC0805FR-0749R9L</t>
+  </si>
+  <si>
+    <t>R7, R9</t>
+  </si>
+  <si>
+    <t>Keramički konenzator</t>
+  </si>
+  <si>
+    <t>22p</t>
+  </si>
+  <si>
+    <t>C8, C28</t>
+  </si>
+  <si>
+    <t>Multilayer Ceramic Capacitors MLCC - SMD/SMT 50V 22pF C0G 0402 1% AEC-Q200</t>
   </si>
   <si>
     <t>KYOCERA AVX</t>
   </si>
   <si>
-    <t>08055C104ZAT2A</t>
-  </si>
-  <si>
-    <t>581-08055C104ZAT2A</t>
-  </si>
-  <si>
-    <t>100p</t>
-  </si>
-  <si>
-    <t>Multilayer Ceramic Capacitors MLCC - SMD/SMT 0805 450V 100pF C0G 5% T:0.6mm</t>
-  </si>
-  <si>
-    <t>C5</t>
-  </si>
-  <si>
-    <t>TDK</t>
-  </si>
-  <si>
-    <t>C2012C0G2W101J060AA</t>
-  </si>
-  <si>
-    <t>810-C2012C0G2W101JAA</t>
-  </si>
-  <si>
-    <t>680p</t>
-  </si>
-  <si>
-    <t>Multilayer Ceramic Capacitors MLCC - SMD/SMT 50V 680pF X7R 0402 1 0% AEC-Q200</t>
-  </si>
-  <si>
-    <t>C8</t>
-  </si>
-  <si>
-    <t>0402</t>
-  </si>
-  <si>
-    <t>KAM05AR71H681KN</t>
-  </si>
-  <si>
-    <t>581-KAM05AR71H681KN</t>
+    <t>KAM05ACG1H220FH</t>
+  </si>
+  <si>
+    <t>581-KAM05ACG1H220FH</t>
   </si>
   <si>
     <t>15p</t>
   </si>
   <si>
+    <t>C10, C11</t>
+  </si>
+  <si>
     <t>CAP CER 15PF 200V NP0 0805</t>
   </si>
   <si>
-    <t>C10, C11</t>
-  </si>
-  <si>
     <t>08052U150JAT2A</t>
   </si>
   <si>
@@ -185,628 +512,283 @@
     <t>10u</t>
   </si>
   <si>
+    <t>C12</t>
+  </si>
+  <si>
+    <t>1210</t>
+  </si>
+  <si>
     <t>Aluminum Electrolytic Capacitor, 10 uF, +/- 20%, -40 to 85 degC, 2-Pin SMD, RoHS, Tape and Reel</t>
   </si>
   <si>
-    <t>C12</t>
-  </si>
-  <si>
-    <t>Yageo Group</t>
-  </si>
-  <si>
     <t>EEV106M035A9DAA</t>
   </si>
   <si>
     <t>80-EEV106M035A9DAA</t>
   </si>
   <si>
+    <t>Zavojnica</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>Power Inductors - SMD 10 UH 20%</t>
+  </si>
+  <si>
+    <t>LSQBA201212T100KR</t>
+  </si>
+  <si>
+    <t>963-SQBA201212T100K</t>
+  </si>
+  <si>
+    <t>10n</t>
+  </si>
+  <si>
+    <t>C5, C25</t>
+  </si>
+  <si>
+    <t>KEMET - C0805C103K5RECAUTO - CAP, AEC-Q200, 0.01UF, 50V, MLCC, 0805</t>
+  </si>
+  <si>
+    <t>C0805C103K5RECAUTO</t>
+  </si>
+  <si>
+    <t>80-C0805C103K5RECAUT</t>
+  </si>
+  <si>
+    <t>L2</t>
+  </si>
+  <si>
+    <t>Fixed Inductors 10nH, 300mA Tol.=+/-5%</t>
+  </si>
+  <si>
+    <t>Abracon</t>
+  </si>
+  <si>
+    <t>AIMC-0805-10NJ-T</t>
+  </si>
+  <si>
+    <t>815-AIMC-0805-10NJT</t>
+  </si>
+  <si>
+    <t>NTC Termistor SMD</t>
+  </si>
+  <si>
+    <t>10k</t>
+  </si>
+  <si>
+    <t>R10</t>
+  </si>
+  <si>
+    <t>NTC (Negative Temperature Coefficient) Thermistors THERMISTOR, NTC 10K OHM, 1%, 0402</t>
+  </si>
+  <si>
+    <t>NTCG103JF103FT1</t>
+  </si>
+  <si>
+    <t>810-NTCG103JF103FT1</t>
+  </si>
+  <si>
+    <t>NTC Termistor TH</t>
+  </si>
+  <si>
+    <t>R21</t>
+  </si>
+  <si>
+    <t>TH-2, 3,7x2,54 mm</t>
+  </si>
+  <si>
+    <t>NTC (Negative Temperature Coefficient) Thermistors 10kohm 1%</t>
+  </si>
+  <si>
+    <t>Semitec</t>
+  </si>
+  <si>
+    <t>103AT-2</t>
+  </si>
+  <si>
+    <t>954-103AT-2</t>
+  </si>
+  <si>
+    <t>R8</t>
+  </si>
+  <si>
+    <t>YAGEO - RC0805JR-0710KL - RES, 10K, 5%, 0.125W, 0805, THICK FILM</t>
+  </si>
+  <si>
+    <t>RC0805JR-0710KL</t>
+  </si>
+  <si>
+    <t>603-RC0805JR-0710KL</t>
+  </si>
+  <si>
+    <t>5k1</t>
+  </si>
+  <si>
+    <t>R12, R14</t>
+  </si>
+  <si>
+    <t>0603</t>
+  </si>
+  <si>
+    <t>Res Thick Film 0603 5.1K Ohm 1% 0.1W(1/10W) ±100ppm/C Pad SMD Automotive T/R</t>
+  </si>
+  <si>
+    <t>AC0603FR-075K1L</t>
+  </si>
+  <si>
+    <t>603-AC0603FR-075K1L</t>
+  </si>
+  <si>
     <t>4u7</t>
   </si>
   <si>
+    <t>C18, C22</t>
+  </si>
+  <si>
     <t>Cap Ceramic 4.7uF 50V X7R 10% Pad SMD 0805 125C T/R</t>
   </si>
   <si>
-    <t>C21, C22</t>
-  </si>
-  <si>
     <t>CGA4J1X7R1H475K125AC</t>
   </si>
   <si>
     <t>810-CGA4J1X7R1H475K1</t>
   </si>
   <si>
+    <t>4R7</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>Thick Film Resistors 1/8W 4.7ohm 1% AEC-Q200</t>
+  </si>
+  <si>
+    <t>AC0805FR-074R7L</t>
+  </si>
+  <si>
+    <t>603-AC0805FR-074R7L</t>
+  </si>
+  <si>
+    <t>3n3</t>
+  </si>
+  <si>
+    <t>L3</t>
+  </si>
+  <si>
+    <t>Fixed Ind 3.3NH 400MA 150MOHM</t>
+  </si>
+  <si>
+    <t>BSCH001005053N3SCS</t>
+  </si>
+  <si>
+    <t>603-BSCH1005053N3SCS</t>
+  </si>
+  <si>
+    <t>2n7</t>
+  </si>
+  <si>
+    <t>L4</t>
+  </si>
+  <si>
+    <t>FIXED IND 2.7NH 300MA 170 MOHM</t>
+  </si>
+  <si>
+    <t>LRC0402CS2N7GV001T</t>
+  </si>
+  <si>
+    <t>609-LRC0402CS2N7GV00</t>
+  </si>
+  <si>
+    <t>2k2</t>
+  </si>
+  <si>
+    <t>R15</t>
+  </si>
+  <si>
+    <t>Res Thick Film 0805 2.2K Ohm 0.1% 0.25W(1/4W) ±50ppm/C Pad SMD Automotive T/R</t>
+  </si>
+  <si>
+    <t>Vishay</t>
+  </si>
+  <si>
+    <t>MCU08050C1501FP500</t>
+  </si>
+  <si>
+    <t>594-MCU08050C1501FP5</t>
+  </si>
+  <si>
+    <t>2k</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>Thick Film Resistors - SMD 2 kOhms 125 mW 0805 1%</t>
+  </si>
+  <si>
+    <t>RC0805FR-102KL</t>
+  </si>
+  <si>
+    <t>603-RC0805FR-102KL</t>
+  </si>
+  <si>
+    <t>R11</t>
+  </si>
+  <si>
+    <t>1u</t>
+  </si>
+  <si>
+    <t>C26, C27</t>
+  </si>
+  <si>
+    <t>Ceramic Capacitor, Multilayer, Ceramic, 50V, 10% +Tol, 10% -Tol, X7R, 15% TC, 1uF, Surface Mount, 0603</t>
+  </si>
+  <si>
+    <t>C1608X7R1H105K080AB</t>
+  </si>
+  <si>
+    <t>810-C1608X7R1H105K08</t>
+  </si>
+  <si>
     <t>1p2</t>
   </si>
   <si>
+    <t>C23</t>
+  </si>
+  <si>
     <t>JOHANSON TECHNOLOGY         500R07S1R2BV4T            MLCC CAPACITOR, 1.2PF, 50V, C0G/NP0, 0.1PF, 0402, FULL REEL</t>
   </si>
   <si>
-    <t>C23</t>
-  </si>
-  <si>
     <t>QSCF500Q1R2B1GV001T</t>
   </si>
   <si>
     <t>609-QSCF500Q1R2B1GV0</t>
   </si>
   <si>
-    <t>10n</t>
-  </si>
-  <si>
-    <t>KEMET - C0805C103K5RECAUTO - CAP, AEC-Q200, 0.01UF, 50V, MLCC, 0805</t>
-  </si>
-  <si>
-    <t>C25</t>
-  </si>
-  <si>
-    <t>C0805C103K5RECAUTO</t>
-  </si>
-  <si>
-    <t>80-C0805C103K5RECAUT</t>
-  </si>
-  <si>
-    <t>1u</t>
-  </si>
-  <si>
-    <t>Ceramic Capacitor, Multilayer, Ceramic, 50V, 10% +Tol, 10% -Tol, X7R, 15% TC, 1uF, Surface Mount, 0603</t>
-  </si>
-  <si>
-    <t>C27</t>
-  </si>
-  <si>
-    <t>0603</t>
-  </si>
-  <si>
-    <t>C1608X7R1H105K080AB</t>
-  </si>
-  <si>
-    <t>810-C1608X7R1H105K08</t>
-  </si>
-  <si>
-    <t>Keramicki konenzator</t>
-  </si>
-  <si>
-    <t>22p</t>
-  </si>
-  <si>
-    <t>Multilayer Ceramic Capacitors MLCC - SMD/SMT 50V 22pF C0G 0402 1% AEC-Q200</t>
-  </si>
-  <si>
-    <t>C28</t>
-  </si>
-  <si>
-    <t>KAM05ACG1H220FH</t>
-  </si>
-  <si>
-    <t>581-KAM05ACG1H220FH</t>
-  </si>
-  <si>
-    <t>Zelena dioda</t>
-  </si>
-  <si>
-    <t>Green</t>
-  </si>
-  <si>
-    <t>Reel / LED, SMD, 0805, 2 Leads, Green, Water Clear Lens, 130 Deg Viewing Angle, Low Current</t>
-  </si>
-  <si>
-    <t>D1, D2</t>
-  </si>
-  <si>
-    <t>Bivar</t>
-  </si>
-  <si>
-    <t>SM0805GCL</t>
-  </si>
-  <si>
-    <t>749-SM0805GCL</t>
-  </si>
-  <si>
-    <t>Feritna perla</t>
-  </si>
-  <si>
-    <t>MPZ2012S601AT000</t>
-  </si>
-  <si>
-    <t>FERRITE BEAD 600 OHM 0805 1LN</t>
-  </si>
-  <si>
-    <t>FB1</t>
-  </si>
-  <si>
-    <t>810-MPZ2012S601AT000</t>
-  </si>
-  <si>
-    <t>IPD</t>
-  </si>
-  <si>
-    <t>MLPF-WB55-01E3</t>
-  </si>
-  <si>
-    <t>RF FILTER, 2.4GHZ TO 2.5GHZ, WLCSP-6;</t>
-  </si>
-  <si>
-    <t>IPD1</t>
-  </si>
-  <si>
-    <t>STMicroelectronics</t>
-  </si>
-  <si>
-    <t>511-MLPF-WB55-01E3</t>
-  </si>
-  <si>
-    <t>USB_C konektor</t>
-  </si>
-  <si>
-    <t>USB4135-GF-A</t>
-  </si>
-  <si>
-    <t>USB Connectors USBC Rec GF RA 6P SMT-SMT stakes 3.16mm</t>
-  </si>
-  <si>
-    <t>J1</t>
-  </si>
-  <si>
-    <t>Global Connector Technology</t>
-  </si>
-  <si>
-    <t>640-USB4135-GF-A</t>
-  </si>
-  <si>
-    <t>Header za bateriju?</t>
-  </si>
-  <si>
-    <t>BAT HEADER 2-1</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>J2</t>
-  </si>
-  <si>
-    <t>Zavojnica</t>
-  </si>
-  <si>
-    <t>Power Inductors - SMD 10 UH 20%</t>
-  </si>
-  <si>
-    <t>L1</t>
-  </si>
-  <si>
-    <t>TAIYO YUDEN</t>
-  </si>
-  <si>
-    <t>LSQBA201212T100KR</t>
-  </si>
-  <si>
-    <t>963-SQBA201212T100K</t>
-  </si>
-  <si>
-    <t>Fixed Inductors 10nH, 300mA Tol.=+/-5%</t>
-  </si>
-  <si>
-    <t>L2</t>
-  </si>
-  <si>
-    <t>Abracon</t>
-  </si>
-  <si>
-    <t>AIMC-0805-10NJ-T</t>
-  </si>
-  <si>
-    <t>815-AIMC-0805-10NJT</t>
-  </si>
-  <si>
-    <t>3n3</t>
-  </si>
-  <si>
-    <t>Fixed Ind 3.3NH 400MA 150MOHM</t>
-  </si>
-  <si>
-    <t>L3</t>
-  </si>
-  <si>
-    <t>BSCH001005053N3SCS</t>
-  </si>
-  <si>
-    <t>603-BSCH1005053N3SCS</t>
-  </si>
-  <si>
-    <t>2n7</t>
-  </si>
-  <si>
-    <t>FIXED IND 2.7NH 300MA 170 MOHM</t>
-  </si>
-  <si>
-    <t>L4</t>
-  </si>
-  <si>
-    <t>LRC0402CS2N7GV001T</t>
-  </si>
-  <si>
-    <t>609-LRC0402CS2N7GV00</t>
-  </si>
-  <si>
-    <t>Otpornik</t>
-  </si>
-  <si>
-    <t>49R9</t>
-  </si>
-  <si>
-    <t>Res Thick Film 0805 49.9 Ohm 1% 0.125W(1/8W) ±100ppm/C Epoxy Pad SMD Automotive T/R</t>
-  </si>
-  <si>
-    <t>R1, R3, R7, R9</t>
-  </si>
-  <si>
-    <t>AC0805FR-0749R9L</t>
-  </si>
-  <si>
-    <t>603-AC0805FR-0749R9L</t>
-  </si>
-  <si>
-    <t>2k</t>
-  </si>
-  <si>
-    <t>Thick Film Resistors - SMD 2 kOhms 125 mW 0805 1%</t>
-  </si>
-  <si>
-    <t>R2, R11</t>
-  </si>
-  <si>
-    <t>RC0805FR-102KL</t>
-  </si>
-  <si>
-    <t>603-RC0805FR-102KL</t>
-  </si>
-  <si>
-    <t>4R7</t>
-  </si>
-  <si>
-    <t>Thick Film Resistors 1/8W 4.7ohm 1% AEC-Q200</t>
-  </si>
-  <si>
-    <t>R4</t>
-  </si>
-  <si>
-    <t>AC0805FR-074R7L</t>
-  </si>
-  <si>
-    <t>603-AC0805FR-074R7L</t>
-  </si>
-  <si>
-    <t>52R3</t>
-  </si>
-  <si>
-    <t>RC0805FR-0752R3L 52,3Ohm</t>
-  </si>
-  <si>
-    <t>R5</t>
-  </si>
-  <si>
-    <t>RC0805FR-0752R3L</t>
-  </si>
-  <si>
-    <t>603-RC0805FR-0752R3L</t>
-  </si>
-  <si>
-    <t>560R</t>
-  </si>
-  <si>
-    <t>Surface Mount Thick Film Resistor, RC Series, 560 ohm, 125 mW, - 1%, 150 V, 0805 [2012 Metric]</t>
-  </si>
-  <si>
-    <t>R6</t>
-  </si>
-  <si>
-    <t>RC0805FR-07560RL</t>
-  </si>
-  <si>
-    <t>603-RC0805FR-07560RL</t>
-  </si>
-  <si>
-    <t>10k</t>
-  </si>
-  <si>
-    <t>YAGEO - RC0805JR-0710KL - RES, 10K, 5%, 0.125W, 0805, THICK FILM</t>
-  </si>
-  <si>
-    <t>R8</t>
-  </si>
-  <si>
-    <t>RC0805JR-0710KL</t>
-  </si>
-  <si>
-    <t>603-RC0805JR-0710KL</t>
-  </si>
-  <si>
-    <t>THERMISTOR NTC 10KOHM 3380K 0402</t>
-  </si>
-  <si>
-    <t>R10</t>
-  </si>
-  <si>
-    <t>NTCG103JF103FT1S</t>
-  </si>
-  <si>
-    <t>810-NTCG103JF103FT1S</t>
-  </si>
-  <si>
-    <t>5k1</t>
-  </si>
-  <si>
-    <t>Res Thick Film 0603 5.1K Ohm 1% 0.1W(1/10W) ±100ppm/C Pad SMD Automotive T/R</t>
-  </si>
-  <si>
-    <t>R12, R14</t>
-  </si>
-  <si>
-    <t>Vishay</t>
-  </si>
-  <si>
-    <t>MCT06030C5101FPW00</t>
-  </si>
-  <si>
-    <t>594-MCT06030C5101FPW</t>
-  </si>
-  <si>
     <t>1k5</t>
   </si>
   <si>
-    <t>Res Thick Film 1206 1.5K Ohm 5% 1/4W ±200ppm/°C Molded SMD SMD Paper T/R</t>
-  </si>
-  <si>
-    <t>R13</t>
-  </si>
-  <si>
-    <t>MCU08050C1501FP500</t>
-  </si>
-  <si>
-    <t>594-MCU08050C1501FP5</t>
-  </si>
-  <si>
-    <t>2k2</t>
-  </si>
-  <si>
-    <t>Res Thick Film 0805 2.2K Ohm 0.1% 0.25W(1/4W) ±50ppm/C Pad SMD Automotive T/R</t>
-  </si>
-  <si>
-    <t>R15</t>
-  </si>
-  <si>
-    <t>MCU08050C2201FP500</t>
-  </si>
-  <si>
-    <t>594-MCU08050C2201FP5</t>
+    <t>R13, R16, R20</t>
+  </si>
+  <si>
+    <t>Thin Film Resistors - SMD 1.5K ohm 1% 50 ppm Thin Film</t>
   </si>
   <si>
     <t>0R0</t>
   </si>
   <si>
-    <t>Ferrite Beads BMC-Q 0402 ZR 0-15R Tol. UH Current</t>
-  </si>
-  <si>
-    <t>R16</t>
-  </si>
-  <si>
-    <t>TE Connectivity / Sigma</t>
-  </si>
-  <si>
-    <t>BMC-Q1E0000M</t>
-  </si>
-  <si>
-    <t>279-BMC-Q1E0000M</t>
-  </si>
-  <si>
-    <t>R17, R18</t>
-  </si>
-  <si>
-    <t>Sklopka</t>
-  </si>
-  <si>
-    <t>TL3301AF160QG</t>
-  </si>
-  <si>
-    <t>Tactile Switches 6mm SMT Gull Wing 5mm Act Height</t>
-  </si>
-  <si>
-    <t>S1</t>
-  </si>
-  <si>
-    <t>E-Switch</t>
-  </si>
-  <si>
-    <t>612-TL3301AF1</t>
-  </si>
-  <si>
-    <t>Buffeer</t>
-  </si>
-  <si>
-    <t>BUF602</t>
-  </si>
-  <si>
-    <t>High Speed Operational Amplifiers High Speed Closed Loop Buffer</t>
-  </si>
-  <si>
-    <t>U1</t>
-  </si>
-  <si>
-    <t>Texas Instruments</t>
-  </si>
-  <si>
-    <t>BUF602ID</t>
-  </si>
-  <si>
-    <t>595-BUF602ID</t>
-  </si>
-  <si>
-    <t>Logaritamsko pojacalo</t>
-  </si>
-  <si>
-    <t>AD8310ARMZ-REEL7</t>
-  </si>
-  <si>
-    <t>SP Amp LOG Amp Single R-R I/P 5.5V 8-Pin MSOP T/R</t>
-  </si>
-  <si>
-    <t>U2</t>
-  </si>
-  <si>
-    <t>MSOP</t>
-  </si>
-  <si>
-    <t>Analog Devices</t>
-  </si>
-  <si>
-    <t>584-AD8310ARMZ-R7</t>
-  </si>
-  <si>
-    <t>Mikrokontroler</t>
-  </si>
-  <si>
-    <t>STM32WB55CGU6</t>
-  </si>
-  <si>
-    <t>MCU 32-Bit STM32WB55 ARM Cortex M4 RISC 1MB Flash 1.7V to 3.6V 48-Pin UFQFPN Tray</t>
-  </si>
-  <si>
-    <t>U3</t>
-  </si>
-  <si>
-    <t>UFQFPN-48</t>
-  </si>
-  <si>
-    <t>511-STM32WB55CGU6</t>
-  </si>
-  <si>
-    <t>Punjac baterije</t>
-  </si>
-  <si>
-    <t>BQ24040DSQR</t>
-  </si>
-  <si>
-    <t>Battery Management 800mA Sng-Inpt Sg Cl Li-Ion Batt Charger A 595-BQ24040DSQT</t>
-  </si>
-  <si>
-    <t>U4</t>
-  </si>
-  <si>
-    <t>595-BQ24040DSQR</t>
-  </si>
-  <si>
-    <t>LDO regulator</t>
-  </si>
-  <si>
-    <t>TPS73633DBVR</t>
-  </si>
-  <si>
-    <t>IC REG LINEAR 3.3V 400MA SOT23-5</t>
-  </si>
-  <si>
-    <t>U5</t>
-  </si>
-  <si>
-    <t>SOT-23</t>
-  </si>
-  <si>
-    <t>595-TPS73633DBVR</t>
-  </si>
-  <si>
-    <t>Schmittov trigger</t>
-  </si>
-  <si>
-    <t>74AHC1G17GWH</t>
-  </si>
-  <si>
-    <t>Buffers &amp; Line Drivers SOT353-1 SNGL TRIGGER BUFFER</t>
-  </si>
-  <si>
-    <t>U6</t>
-  </si>
-  <si>
-    <t>Nexperia</t>
-  </si>
-  <si>
-    <t>771-74AHC1G17GWH</t>
-  </si>
-  <si>
-    <t>SMA konektor</t>
-  </si>
-  <si>
-    <t>60312002114503</t>
-  </si>
-  <si>
-    <t>Supplied in a Tray, Wurth Elektronik Straight PCB Mount SMA Connector, Solder Termination</t>
-  </si>
-  <si>
-    <t>X1</t>
-  </si>
-  <si>
-    <t>Wurth Elektronik</t>
-  </si>
-  <si>
-    <t>710-60312002114503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Header </t>
-  </si>
-  <si>
-    <t>HDR 1X4</t>
-  </si>
-  <si>
-    <t>CONN HEADER VERT 4POS 2.54MM</t>
-  </si>
-  <si>
-    <t>X2</t>
-  </si>
-  <si>
-    <t>Amphenol Communications Solutions</t>
-  </si>
-  <si>
-    <t>68001-204HLF</t>
-  </si>
-  <si>
-    <t>649-68001-204HLF</t>
-  </si>
-  <si>
-    <t>Kristalni oscilator</t>
-  </si>
-  <si>
-    <t>NX2016SA-32MHz</t>
-  </si>
-  <si>
-    <t>Crystal 32MHZ 6PF SMD</t>
-  </si>
-  <si>
-    <t>Y1</t>
-  </si>
-  <si>
-    <t>NDK</t>
-  </si>
-  <si>
-    <t>NX2016SA-32M-EXS00A-CS06465</t>
-  </si>
-  <si>
-    <t>344-NX2016SA32S06465</t>
-  </si>
-  <si>
-    <t>NX2012SA-32.768kHz</t>
-  </si>
-  <si>
-    <t>CRYSTAL 32.768KHZ 6PF SMD</t>
-  </si>
-  <si>
-    <t>Y2</t>
-  </si>
-  <si>
-    <t>SMD/SMT</t>
-  </si>
-  <si>
-    <t>NX2012SA-32.768K-STD-MUB-1</t>
-  </si>
-  <si>
-    <t>344-NX2012SA32768K1</t>
+    <t>R6, R17, R18, R19</t>
+  </si>
+  <si>
+    <t>Thick Film Resistors - SMD 1/8 Watt ZEROohm Jumper</t>
+  </si>
+  <si>
+    <t>CRCW06030000Z0EAHP</t>
+  </si>
+  <si>
+    <t>71-CRCW06030000Z0EAH</t>
   </si>
 </sst>
 </file>
@@ -1202,14 +1184,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A0F86D1-A5F9-42C4-9426-6EEF649C0F2E}">
-  <dimension ref="A1:L44"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{118BCAE6-AC2B-416B-85FB-CD78990740B3}">
+  <dimension ref="A1:L42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="21.5703125" customWidth="1"/>
-    <col min="3" max="4" width="16.5703125" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" customWidth="1"/>
+    <col min="3" max="3" width="21.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" customWidth="1"/>
     <col min="6" max="6" width="16.85546875" customWidth="1"/>
     <col min="7" max="7" width="27.42578125" customWidth="1"/>
     <col min="8" max="8" width="19.140625" customWidth="1"/>
@@ -1286,13 +1269,13 @@
         <v>19</v>
       </c>
       <c r="J2" s="1">
-        <v>1.3</v>
+        <v>0.57977999999999996</v>
       </c>
       <c r="K2" s="1">
         <v>1</v>
       </c>
       <c r="L2" s="1">
-        <v>1.3</v>
+        <v>0.57977999999999996</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -1315,27 +1298,27 @@
         <v>25</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="J3" s="1">
-        <v>0.13491</v>
+        <v>2.14</v>
       </c>
       <c r="K3" s="1">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="L3" s="1">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>28</v>
@@ -1347,13 +1330,13 @@
         <v>30</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>18</v>
@@ -1362,1499 +1345,1445 @@
         <v>33</v>
       </c>
       <c r="J4" s="1">
-        <v>0.15368999999999999</v>
+        <v>0.29842000000000002</v>
       </c>
       <c r="K4" s="1">
         <v>1</v>
       </c>
       <c r="L4" s="1">
-        <v>0.15368999999999999</v>
+        <v>0.29842000000000002</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="H5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" s="1">
-        <v>0.29885</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="J5" s="1"/>
       <c r="K5" s="1">
         <v>1</v>
       </c>
-      <c r="L5" s="1">
-        <v>0.29885</v>
-      </c>
+      <c r="L5" s="1"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J6" s="1">
-        <v>0.26468999999999998</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="J6" s="1"/>
       <c r="K6" s="1">
-        <v>2</v>
-      </c>
-      <c r="L6" s="1">
-        <v>0.52939000000000003</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L6" s="1"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="G7" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J7" s="1">
-        <v>0.27322999999999997</v>
+        <v>0.72472999999999999</v>
       </c>
       <c r="K7" s="1">
         <v>1</v>
       </c>
       <c r="L7" s="1">
-        <v>0.27322999999999997</v>
+        <v>0.72472999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J8" s="1">
-        <v>0.46107999999999999</v>
+        <v>9.3789999999999998E-2</v>
       </c>
       <c r="K8" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L8" s="1">
-        <v>0.92215999999999998</v>
+        <v>9.3789999999999998E-2</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="J9" s="1">
-        <v>0.13661999999999999</v>
+        <v>0.31546999999999997</v>
       </c>
       <c r="K9" s="1">
         <v>1</v>
       </c>
       <c r="L9" s="1">
-        <v>0.13661999999999999</v>
+        <v>0.31546999999999997</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="J10" s="1">
-        <v>0.21346000000000001</v>
+        <v>0.14495</v>
       </c>
       <c r="K10" s="1">
         <v>1</v>
       </c>
       <c r="L10" s="1">
-        <v>0.21346000000000001</v>
+        <v>0.14495</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="J11" s="1">
-        <v>0.17931</v>
+        <v>0.38368000000000002</v>
       </c>
       <c r="K11" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L11" s="1">
-        <v>0.17931</v>
+        <v>1.1499999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>37</v>
+        <v>85</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="J12" s="1">
-        <v>0.27322999999999997</v>
+        <v>5.77</v>
       </c>
       <c r="K12" s="1">
         <v>1</v>
       </c>
       <c r="L12" s="1">
-        <v>0.27322999999999997</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>83</v>
+        <v>25</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="J13" s="1">
-        <v>0.47815999999999997</v>
+        <v>0.78441000000000005</v>
       </c>
       <c r="K13" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L13" s="1">
-        <v>0.95630999999999999</v>
+        <v>0.78441000000000005</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="J14" s="1">
-        <v>9.3920000000000003E-2</v>
+        <v>12.23</v>
       </c>
       <c r="K14" s="1">
         <v>1</v>
       </c>
       <c r="L14" s="1">
-        <v>9.3920000000000003E-2</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E15" s="1"/>
+        <v>105</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>106</v>
+      </c>
       <c r="F15" s="2" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="J15" s="1">
-        <v>0.31591999999999998</v>
+        <v>1.3</v>
       </c>
       <c r="K15" s="1">
         <v>1</v>
       </c>
       <c r="L15" s="1">
-        <v>0.31591999999999998</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E16" s="1"/>
+        <v>112</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>113</v>
+      </c>
       <c r="F16" s="2" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="J16" s="1">
-        <v>0.58062000000000002</v>
+        <v>0.10231</v>
       </c>
       <c r="K16" s="1">
         <v>1</v>
       </c>
       <c r="L16" s="1">
-        <v>0.58062000000000002</v>
+        <v>0.10231</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>122</v>
+      </c>
       <c r="J17" s="1"/>
       <c r="K17" s="1">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="L17" s="1"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>46</v>
+        <v>124</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>109</v>
+        <v>44</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>24</v>
+        <v>126</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="J18" s="1">
-        <v>9.3920000000000003E-2</v>
+        <v>0.11083999999999999</v>
       </c>
       <c r="K18" s="1">
         <v>1</v>
       </c>
       <c r="L18" s="1">
-        <v>9.3920000000000003E-2</v>
+        <v>0.11083999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>62</v>
+        <v>130</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>114</v>
+        <v>44</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>24</v>
+        <v>132</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="J19" s="1">
-        <v>0.10246</v>
+        <v>8.5260000000000002E-2</v>
       </c>
       <c r="K19" s="1">
         <v>1</v>
       </c>
       <c r="L19" s="1">
-        <v>0.10246</v>
+        <v>8.5260000000000002E-2</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>49</v>
+        <v>133</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="J20" s="1">
-        <v>8.5389999999999994E-2</v>
+        <v>8.7200000000000003E-3</v>
       </c>
       <c r="K20" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L20" s="1">
-        <v>8.5389999999999994E-2</v>
+        <v>8.7239999999999998E-2</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>17</v>
+        <v>133</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="J21" s="1">
-        <v>8.5389999999999994E-2</v>
+        <v>8.7200000000000003E-3</v>
       </c>
       <c r="K21" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L21" s="1">
-        <v>8.5389999999999994E-2</v>
+        <v>8.7239999999999998E-2</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>49</v>
+        <v>146</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="J22" s="1">
-        <v>1.025E-2</v>
+        <v>0.27284000000000003</v>
       </c>
       <c r="K22" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L22" s="1">
-        <v>0.10246</v>
+        <v>0.54568000000000005</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>136</v>
+        <v>44</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>24</v>
+        <v>151</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>49</v>
+        <v>146</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="J23" s="1">
-        <v>5.9800000000000001E-3</v>
+        <v>0.26430999999999999</v>
       </c>
       <c r="K23" s="1">
         <v>2</v>
       </c>
       <c r="L23" s="1">
-        <v>5.9769999999999997E-2</v>
+        <v>0.52863000000000004</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>24</v>
+        <v>158</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>49</v>
+        <v>133</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="J24" s="1">
-        <v>9.3920000000000003E-2</v>
+        <v>0.34105000000000002</v>
       </c>
       <c r="K24" s="1">
         <v>1</v>
       </c>
       <c r="L24" s="1">
-        <v>9.3920000000000003E-2</v>
+        <v>0.34105000000000002</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>128</v>
+        <v>161</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>146</v>
+        <v>44</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>24</v>
+        <v>163</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="J25" s="1">
-        <v>8.5389999999999994E-2</v>
+        <v>9.3789999999999998E-2</v>
       </c>
       <c r="K25" s="1">
         <v>1</v>
       </c>
       <c r="L25" s="1">
-        <v>8.5389999999999994E-2</v>
+        <v>9.3789999999999998E-2</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>151</v>
+        <v>44</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>24</v>
+        <v>168</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>49</v>
+        <v>133</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="J26" s="1">
-        <v>8.5389999999999994E-2</v>
+        <v>0.21315999999999999</v>
       </c>
       <c r="K26" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L26" s="1">
-        <v>8.5389999999999994E-2</v>
+        <v>0.42631000000000002</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>128</v>
+        <v>161</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>156</v>
+        <v>44</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>24</v>
+        <v>172</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>49</v>
+        <v>173</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="J27" s="1">
-        <v>8.5389999999999994E-2</v>
+        <v>0.10231</v>
       </c>
       <c r="K27" s="1">
         <v>1</v>
       </c>
       <c r="L27" s="1">
-        <v>8.5389999999999994E-2</v>
+        <v>0.10231</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>128</v>
+        <v>176</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>160</v>
+        <v>112</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>37</v>
+        <v>179</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="J28" s="1">
-        <v>9.3920000000000003E-2</v>
+        <v>8.5260000000000002E-2</v>
       </c>
       <c r="K28" s="1">
         <v>1</v>
       </c>
       <c r="L28" s="1">
-        <v>9.3920000000000003E-2</v>
+        <v>8.5260000000000002E-2</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>128</v>
+        <v>182</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>70</v>
+        <v>185</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="J29" s="1">
-        <v>0.13661999999999999</v>
+        <v>0.49452000000000002</v>
       </c>
       <c r="K29" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L29" s="1">
-        <v>0.27322999999999997</v>
+        <v>0.49452000000000002</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>171</v>
+        <v>44</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>24</v>
+        <v>190</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>166</v>
+        <v>133</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="J30" s="1">
-        <v>8.5389999999999994E-2</v>
+        <v>8.5260000000000002E-2</v>
       </c>
       <c r="K30" s="1">
         <v>1</v>
       </c>
       <c r="L30" s="1">
-        <v>8.5389999999999994E-2</v>
+        <v>8.5260000000000002E-2</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>24</v>
+        <v>196</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>166</v>
+        <v>133</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="J31" s="1">
-        <v>8.5389999999999994E-2</v>
+        <v>1.023E-2</v>
       </c>
       <c r="K31" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L31" s="1">
-        <v>8.5389999999999994E-2</v>
+        <v>0.10231</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>181</v>
+        <v>44</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>37</v>
+        <v>201</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>182</v>
+        <v>59</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="J32" s="1">
-        <v>0.13661999999999999</v>
+        <v>0.47747000000000001</v>
       </c>
       <c r="K32" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L32" s="1">
-        <v>0.27322999999999997</v>
+        <v>0.95494000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>185</v>
+        <v>44</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>37</v>
+        <v>206</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>182</v>
+        <v>133</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="J33" s="1">
-        <v>0.13661999999999999</v>
+        <v>9.3789999999999998E-2</v>
       </c>
       <c r="K33" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L33" s="1">
-        <v>0.27322999999999997</v>
+        <v>9.3789999999999998E-2</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E34" s="1"/>
+        <v>112</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>211</v>
+      </c>
       <c r="F34" s="2" t="s">
-        <v>190</v>
+        <v>133</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="J34" s="1">
-        <v>0.29885</v>
+        <v>8.5260000000000002E-2</v>
       </c>
       <c r="K34" s="1">
         <v>1</v>
       </c>
       <c r="L34" s="1">
-        <v>0.29885</v>
+        <v>8.5260000000000002E-2</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="E35" s="1"/>
+        <v>112</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>216</v>
+      </c>
       <c r="F35" s="2" t="s">
-        <v>196</v>
+        <v>107</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="J35" s="1">
-        <v>5.78</v>
+        <v>8.5260000000000002E-2</v>
       </c>
       <c r="K35" s="1">
         <v>1</v>
       </c>
       <c r="L35" s="1">
-        <v>5.78</v>
+        <v>8.5260000000000002E-2</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="J36" s="1">
-        <v>12.01</v>
+        <v>8.5260000000000002E-2</v>
       </c>
       <c r="K36" s="1">
         <v>1</v>
       </c>
       <c r="L36" s="1">
-        <v>12.01</v>
+        <v>8.5260000000000002E-2</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>206</v>
+        <v>129</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>209</v>
+        <v>44</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="J37" s="1"/>
+        <v>229</v>
+      </c>
+      <c r="J37" s="1">
+        <v>7.2700000000000001E-2</v>
+      </c>
       <c r="K37" s="1">
         <v>1</v>
       </c>
-      <c r="L37" s="1"/>
+      <c r="L37" s="1">
+        <v>7.2700000000000001E-2</v>
+      </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>212</v>
+        <v>129</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="E38" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>227</v>
+      </c>
       <c r="F38" s="2" t="s">
-        <v>196</v>
+        <v>133</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="J38" s="1">
-        <v>0.78554000000000002</v>
+        <v>7.2700000000000001E-2</v>
       </c>
       <c r="K38" s="1">
         <v>1</v>
       </c>
       <c r="L38" s="1">
-        <v>0.78554000000000002</v>
+        <v>7.2700000000000001E-2</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>217</v>
+        <v>109</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>196</v>
+        <v>59</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="J39" s="1">
-        <v>2.08</v>
+        <v>0.18758</v>
       </c>
       <c r="K39" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L39" s="1">
-        <v>2.08</v>
+        <v>0.37514999999999998</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>223</v>
+        <v>109</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>226</v>
+        <v>112</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>24</v>
+        <v>238</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>227</v>
+        <v>107</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="J40" s="1">
-        <v>0.111</v>
+        <v>0.13642000000000001</v>
       </c>
       <c r="K40" s="1">
         <v>1</v>
       </c>
       <c r="L40" s="1">
-        <v>0.111</v>
+        <v>0.13642000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>229</v>
+        <v>129</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="E41" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>243</v>
+      </c>
       <c r="F41" s="2" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="J41" s="1">
-        <v>4.92</v>
+        <v>8.5260000000000002E-2</v>
       </c>
       <c r="K41" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L41" s="1">
-        <v>4.92</v>
+        <v>0.25579000000000002</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>235</v>
+        <v>129</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="E42" s="1"/>
+        <v>195</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>246</v>
+      </c>
       <c r="F42" s="2" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="J42" s="1">
-        <v>0.34154000000000001</v>
+        <v>2.6429999999999999E-2</v>
       </c>
       <c r="K42" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L42" s="1">
-        <v>0.34154000000000001</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="J43" s="1">
-        <v>0.49523</v>
-      </c>
-      <c r="K43" s="1">
-        <v>1</v>
-      </c>
-      <c r="L43" s="1">
-        <v>0.49523</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="J44" s="1">
-        <v>0.72577000000000003</v>
-      </c>
-      <c r="K44" s="1">
-        <v>1</v>
-      </c>
-      <c r="L44" s="1">
-        <v>0.72577000000000003</v>
+        <v>0.26430999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/IBC_prijamnik_VB/Project Outputs for IBC_prijamnik_VB/IBC_prijamnik_VB.xlsx
+++ b/IBC_prijamnik_VB/Project Outputs for IBC_prijamnik_VB/IBC_prijamnik_VB.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FER\3. godina\6. sem\ZAVRŠNI\IBC_prijamnik_VB\Project Outputs for IBC_prijamnik_VB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FER\3. godina\6. sem\zavrsni\IBC_prijamnik_VB\Project Outputs for IBC_prijamnik_VB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E72880B1-1C97-4E22-B62C-FBCAB99DC35D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EA31E35-0053-4E73-A55C-6952F13619E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3B52401C-5D40-4D8F-ACA8-50DFA55B882D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{867B591F-A776-498A-A398-4FBA2AE2CBA0}"/>
   </bookViews>
   <sheets>
     <sheet name="IBC_prijamnik_VB" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="237">
   <si>
     <t>Komponenta</t>
   </si>
@@ -674,7 +674,7 @@
     <t>LRC0402CS2N7GV001T</t>
   </si>
   <si>
-    <t>609-L-07C2N7SV6T</t>
+    <t>712-LRC0402CS2N7GV001TCT-ND</t>
   </si>
   <si>
     <t>2k2</t>
@@ -743,10 +743,13 @@
     <t>R6, R18, R19</t>
   </si>
   <si>
-    <t>CRCW06030000Z0EAHP</t>
-  </si>
-  <si>
-    <t>71-CRCW06030000Z0EAH</t>
+    <t>Walsin Technologies</t>
+  </si>
+  <si>
+    <t>MR04X000PTL</t>
+  </si>
+  <si>
+    <t>791-MR04X000PTL</t>
   </si>
   <si>
     <t>R17</t>
@@ -762,7 +765,6 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <charset val="238"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1146,25 +1148,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B6FA728-A898-4033-8B72-B0C3E39DD8AC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0C52A4C-1683-4AAB-9328-2BF4BEE52630}">
   <dimension ref="A1:L41"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" customWidth="1"/>
-    <col min="2" max="2" width="20.88671875" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="16.33203125" customWidth="1"/>
-    <col min="7" max="7" width="26.44140625" customWidth="1"/>
-    <col min="8" max="8" width="18.5546875" customWidth="1"/>
-    <col min="9" max="9" width="22.33203125" customWidth="1"/>
-    <col min="10" max="10" width="20.109375" customWidth="1"/>
-    <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="19.33203125" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" customWidth="1"/>
+    <col min="3" max="3" width="21.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" customWidth="1"/>
+    <col min="7" max="7" width="27.42578125" customWidth="1"/>
+    <col min="8" max="8" width="19.140625" customWidth="1"/>
+    <col min="9" max="9" width="23.140625" customWidth="1"/>
+    <col min="10" max="10" width="20.85546875" customWidth="1"/>
+    <col min="11" max="11" width="11.28515625" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1202,7 +1204,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
@@ -1231,16 +1233,16 @@
         <v>19</v>
       </c>
       <c r="J2" s="1">
-        <v>0.58231999999999995</v>
+        <v>0.57786999999999999</v>
       </c>
       <c r="K2" s="1">
         <v>1</v>
       </c>
       <c r="L2" s="1">
-        <v>0.58231999999999995</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+        <v>0.57786999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>20</v>
       </c>
@@ -1269,16 +1271,16 @@
         <v>26</v>
       </c>
       <c r="J3" s="1">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="K3" s="1">
         <v>1</v>
       </c>
       <c r="L3" s="1">
-        <v>2.15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+        <v>2.13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
@@ -1307,16 +1309,16 @@
         <v>33</v>
       </c>
       <c r="J4" s="1">
-        <v>0.29971999999999999</v>
+        <v>0.29743000000000003</v>
       </c>
       <c r="K4" s="1">
         <v>1</v>
       </c>
       <c r="L4" s="1">
-        <v>0.29971999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+        <v>0.29743000000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>34</v>
       </c>
@@ -1350,7 +1352,7 @@
       </c>
       <c r="L5" s="1"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>41</v>
       </c>
@@ -1384,7 +1386,7 @@
       </c>
       <c r="L6" s="1"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>41</v>
       </c>
@@ -1413,16 +1415,16 @@
         <v>54</v>
       </c>
       <c r="J7" s="1">
-        <v>0.72789999999999999</v>
+        <v>0.72233999999999998</v>
       </c>
       <c r="K7" s="1">
         <v>1</v>
       </c>
       <c r="L7" s="1">
-        <v>0.72789999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+        <v>0.72233999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>55</v>
       </c>
@@ -1451,16 +1453,16 @@
         <v>60</v>
       </c>
       <c r="J8" s="1">
-        <v>9.4200000000000006E-2</v>
+        <v>9.3479999999999994E-2</v>
       </c>
       <c r="K8" s="1">
         <v>1</v>
       </c>
       <c r="L8" s="1">
-        <v>9.4200000000000006E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+        <v>9.3479999999999994E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>61</v>
       </c>
@@ -1489,16 +1491,16 @@
         <v>66</v>
       </c>
       <c r="J9" s="1">
-        <v>0.31685000000000002</v>
+        <v>0.31442999999999999</v>
       </c>
       <c r="K9" s="1">
         <v>1</v>
       </c>
       <c r="L9" s="1">
-        <v>0.31685000000000002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+        <v>0.31442999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>27</v>
       </c>
@@ -1527,16 +1529,16 @@
         <v>73</v>
       </c>
       <c r="J10" s="1">
-        <v>0.34254000000000001</v>
+        <v>0.33992</v>
       </c>
       <c r="K10" s="1">
         <v>1</v>
       </c>
       <c r="L10" s="1">
-        <v>0.34254000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+        <v>0.33992</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>74</v>
       </c>
@@ -1570,7 +1572,7 @@
       </c>
       <c r="L11" s="1"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>81</v>
       </c>
@@ -1599,16 +1601,16 @@
         <v>86</v>
       </c>
       <c r="J12" s="1">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="K12" s="1">
         <v>1</v>
       </c>
       <c r="L12" s="1">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>87</v>
       </c>
@@ -1637,16 +1639,16 @@
         <v>92</v>
       </c>
       <c r="J13" s="1">
-        <v>0.78783999999999998</v>
+        <v>0.78183000000000002</v>
       </c>
       <c r="K13" s="1">
         <v>1</v>
       </c>
       <c r="L13" s="1">
-        <v>0.78783999999999998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+        <v>0.78183000000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>93</v>
       </c>
@@ -1675,16 +1677,16 @@
         <v>99</v>
       </c>
       <c r="J14" s="1">
-        <v>12.28</v>
+        <v>12.19</v>
       </c>
       <c r="K14" s="1">
         <v>1</v>
       </c>
       <c r="L14" s="1">
-        <v>12.28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+        <v>12.19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>100</v>
       </c>
@@ -1713,16 +1715,16 @@
         <v>106</v>
       </c>
       <c r="J15" s="1">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="K15" s="1">
         <v>1</v>
       </c>
       <c r="L15" s="1">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>107</v>
       </c>
@@ -1751,16 +1753,16 @@
         <v>114</v>
       </c>
       <c r="J16" s="1">
-        <v>0.10276</v>
+        <v>0.10198</v>
       </c>
       <c r="K16" s="1">
         <v>1</v>
       </c>
       <c r="L16" s="1">
-        <v>0.10276</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+        <v>0.10198</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>107</v>
       </c>
@@ -1794,7 +1796,7 @@
       </c>
       <c r="L17" s="1"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>121</v>
       </c>
@@ -1823,16 +1825,16 @@
         <v>126</v>
       </c>
       <c r="J18" s="1">
-        <v>0.11133</v>
+        <v>0.11047999999999999</v>
       </c>
       <c r="K18" s="1">
         <v>1</v>
       </c>
       <c r="L18" s="1">
-        <v>0.11133</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+        <v>0.11047999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>127</v>
       </c>
@@ -1861,16 +1863,16 @@
         <v>133</v>
       </c>
       <c r="J19" s="1">
-        <v>8.5629999999999998E-2</v>
+        <v>8.498E-2</v>
       </c>
       <c r="K19" s="1">
         <v>1</v>
       </c>
       <c r="L19" s="1">
-        <v>8.5629999999999998E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+        <v>8.498E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>127</v>
       </c>
@@ -1899,16 +1901,16 @@
         <v>138</v>
       </c>
       <c r="J20" s="1">
-        <v>1.0279999999999999E-2</v>
+        <v>1.0200000000000001E-2</v>
       </c>
       <c r="K20" s="1">
         <v>4</v>
       </c>
       <c r="L20" s="1">
-        <v>0.10276</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+        <v>0.10198</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>107</v>
       </c>
@@ -1937,16 +1939,16 @@
         <v>144</v>
       </c>
       <c r="J21" s="1">
-        <v>0.27403</v>
+        <v>0.27194000000000002</v>
       </c>
       <c r="K21" s="1">
         <v>2</v>
       </c>
       <c r="L21" s="1">
-        <v>0.54805999999999999</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+        <v>0.54388000000000003</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>107</v>
       </c>
@@ -1975,16 +1977,16 @@
         <v>149</v>
       </c>
       <c r="J22" s="1">
-        <v>0.26546999999999998</v>
+        <v>0.26344000000000001</v>
       </c>
       <c r="K22" s="1">
         <v>2</v>
       </c>
       <c r="L22" s="1">
-        <v>0.53093999999999997</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+        <v>0.52688000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>150</v>
       </c>
@@ -2013,16 +2015,16 @@
         <v>156</v>
       </c>
       <c r="J23" s="1">
-        <v>0.29971999999999999</v>
+        <v>0.29743000000000003</v>
       </c>
       <c r="K23" s="1">
         <v>1</v>
       </c>
       <c r="L23" s="1">
-        <v>0.29971999999999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+        <v>0.29743000000000003</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>157</v>
       </c>
@@ -2051,16 +2053,16 @@
         <v>162</v>
       </c>
       <c r="J24" s="1">
-        <v>9.4200000000000006E-2</v>
+        <v>9.3479999999999994E-2</v>
       </c>
       <c r="K24" s="1">
         <v>1</v>
       </c>
       <c r="L24" s="1">
-        <v>9.4200000000000006E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+        <v>9.3479999999999994E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>107</v>
       </c>
@@ -2089,16 +2091,16 @@
         <v>167</v>
       </c>
       <c r="J25" s="1">
-        <v>0.21409</v>
+        <v>0.21245</v>
       </c>
       <c r="K25" s="1">
         <v>2</v>
       </c>
       <c r="L25" s="1">
-        <v>0.42817</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+        <v>0.42491000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>157</v>
       </c>
@@ -2127,16 +2129,16 @@
         <v>172</v>
       </c>
       <c r="J26" s="1">
-        <v>0.10276</v>
+        <v>0.10198</v>
       </c>
       <c r="K26" s="1">
         <v>1</v>
       </c>
       <c r="L26" s="1">
-        <v>0.10276</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+        <v>0.10198</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>173</v>
       </c>
@@ -2165,16 +2167,16 @@
         <v>178</v>
       </c>
       <c r="J27" s="1">
-        <v>8.5629999999999998E-2</v>
+        <v>8.498E-2</v>
       </c>
       <c r="K27" s="1">
         <v>1</v>
       </c>
       <c r="L27" s="1">
-        <v>8.5629999999999998E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+        <v>8.498E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>173</v>
       </c>
@@ -2212,7 +2214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>127</v>
       </c>
@@ -2241,16 +2243,16 @@
         <v>187</v>
       </c>
       <c r="J29" s="1">
-        <v>8.5629999999999998E-2</v>
+        <v>0.18695999999999999</v>
       </c>
       <c r="K29" s="1">
         <v>1</v>
       </c>
       <c r="L29" s="1">
-        <v>8.5629999999999998E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+        <v>0.18695999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>127</v>
       </c>
@@ -2279,16 +2281,16 @@
         <v>193</v>
       </c>
       <c r="J30" s="1">
-        <v>1.0279999999999999E-2</v>
+        <v>1.0200000000000001E-2</v>
       </c>
       <c r="K30" s="1">
         <v>2</v>
       </c>
       <c r="L30" s="1">
-        <v>0.10276</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+        <v>0.10198</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>107</v>
       </c>
@@ -2317,16 +2319,16 @@
         <v>197</v>
       </c>
       <c r="J31" s="1">
-        <v>0.47955999999999999</v>
+        <v>0.47588999999999998</v>
       </c>
       <c r="K31" s="1">
         <v>2</v>
       </c>
       <c r="L31" s="1">
-        <v>0.95911000000000002</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+        <v>0.95179000000000002</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>127</v>
       </c>
@@ -2355,16 +2357,16 @@
         <v>201</v>
       </c>
       <c r="J32" s="1">
-        <v>9.4200000000000006E-2</v>
+        <v>9.3479999999999994E-2</v>
       </c>
       <c r="K32" s="1">
         <v>1</v>
       </c>
       <c r="L32" s="1">
-        <v>9.4200000000000006E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+        <v>9.3479999999999994E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>157</v>
       </c>
@@ -2394,7 +2396,7 @@
       </c>
       <c r="L33" s="1"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>157</v>
       </c>
@@ -2417,18 +2419,22 @@
         <v>209</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="J34" s="1"/>
+      <c r="J34" s="1">
+        <v>8.498E-2</v>
+      </c>
       <c r="K34" s="1">
         <v>1</v>
       </c>
-      <c r="L34" s="1"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L34" s="1">
+        <v>8.498E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>127</v>
       </c>
@@ -2457,16 +2463,16 @@
         <v>215</v>
       </c>
       <c r="J35" s="1">
-        <v>7.3330000000000006E-2</v>
+        <v>7.2220000000000006E-2</v>
       </c>
       <c r="K35" s="1">
         <v>1</v>
       </c>
       <c r="L35" s="1">
-        <v>7.3330000000000006E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+        <v>7.2220000000000006E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>127</v>
       </c>
@@ -2495,16 +2501,16 @@
         <v>219</v>
       </c>
       <c r="J36" s="1">
-        <v>5.9899999999999997E-3</v>
+        <v>5.9500000000000004E-3</v>
       </c>
       <c r="K36" s="1">
         <v>2</v>
       </c>
       <c r="L36" s="1">
-        <v>5.994E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+        <v>5.9490000000000001E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>107</v>
       </c>
@@ -2533,16 +2539,16 @@
         <v>223</v>
       </c>
       <c r="J37" s="1">
-        <v>0.18840000000000001</v>
+        <v>0.18695999999999999</v>
       </c>
       <c r="K37" s="1">
         <v>2</v>
       </c>
       <c r="L37" s="1">
-        <v>0.37679000000000001</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+        <v>0.37391999999999997</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>107</v>
       </c>
@@ -2571,16 +2577,16 @@
         <v>227</v>
       </c>
       <c r="J38" s="1">
-        <v>0.13702</v>
+        <v>0.13597000000000001</v>
       </c>
       <c r="K38" s="1">
         <v>1</v>
       </c>
       <c r="L38" s="1">
-        <v>0.13702</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+        <v>0.13597000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>127</v>
       </c>
@@ -2609,16 +2615,16 @@
         <v>215</v>
       </c>
       <c r="J39" s="1">
-        <v>7.3330000000000006E-2</v>
+        <v>7.2220000000000006E-2</v>
       </c>
       <c r="K39" s="1">
         <v>3</v>
       </c>
       <c r="L39" s="1">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+        <v>0.21665000000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>127</v>
       </c>
@@ -2629,34 +2635,34 @@
         <v>232</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>190</v>
+        <v>110</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>130</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J40" s="1">
-        <v>8.5629999999999998E-2</v>
+        <v>3.4840000000000003E-2</v>
       </c>
       <c r="K40" s="1">
         <v>3</v>
       </c>
       <c r="L40" s="1">
-        <v>0.25690000000000002</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+        <v>0.34842000000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>127</v>
       </c>
@@ -2664,34 +2670,34 @@
         <v>231</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>190</v>
+        <v>110</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>130</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J41" s="1">
-        <v>8.5629999999999998E-2</v>
+        <v>3.4840000000000003E-2</v>
       </c>
       <c r="K41" s="1">
         <v>0</v>
       </c>
       <c r="L41" s="1">
-        <v>0.25690000000000002</v>
+        <v>0.34842000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/IBC_prijamnik_VB/Project Outputs for IBC_prijamnik_VB/IBC_prijamnik_VB.xlsx
+++ b/IBC_prijamnik_VB/Project Outputs for IBC_prijamnik_VB/IBC_prijamnik_VB.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FER\3godina\6sem\zavrsni\IBC_prijamnik_VB\Project Outputs for IBC_prijamnik_VB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FER\3. godina\6. sem\zavrsni\IBC_prijamnik_VB\Project Outputs for IBC_prijamnik_VB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{131F1DE7-E9CF-4D18-A12D-053BD0F1ECA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7EDBB704-C8E0-4F03-8B83-DD0CB123DCB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FC20390B-C3EB-445D-974D-672AACE236C8}"/>
+    <workbookView xWindow="8820" yWindow="4815" windowWidth="28800" windowHeight="15345" xr2:uid="{5636603A-DEFA-48BC-8903-7E90C53F8C7C}"/>
   </bookViews>
   <sheets>
     <sheet name="IBC_prijamnik_VB" sheetId="1" r:id="rId1"/>
@@ -42,53 +42,53 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="223">
+  <si>
+    <t>Vrijednost</t>
+  </si>
   <si>
     <t>Oznaka komponente</t>
   </si>
   <si>
-    <t>Vrijednost</t>
+    <t>Kucište</t>
   </si>
   <si>
     <t>Opis</t>
   </si>
   <si>
-    <t>Kučište</t>
-  </si>
-  <si>
-    <t>Proizvodač</t>
-  </si>
-  <si>
-    <t>Oznaka proizvodača</t>
-  </si>
-  <si>
-    <t>Dobavljač</t>
-  </si>
-  <si>
-    <t>Oznaka dobavljača</t>
+    <t>Proizvodac</t>
+  </si>
+  <si>
+    <t>Oznaka proizvodaca</t>
+  </si>
+  <si>
+    <t>Dobavljac</t>
+  </si>
+  <si>
+    <t>Oznaka dobavljaca</t>
   </si>
   <si>
     <t>Cijena komponente (EUR)</t>
   </si>
   <si>
-    <t>Količina</t>
+    <t>Kolicina</t>
   </si>
   <si>
     <t>Ukupna cijena (EUR)</t>
   </si>
   <si>
+    <t>2450AT18B100E</t>
+  </si>
+  <si>
     <t>A1</t>
   </si>
   <si>
-    <t>2450AT18B100E</t>
+    <t>SMD-2, 3,8x1,8mm</t>
   </si>
   <si>
     <t>Antena, 2.45GHz</t>
   </si>
   <si>
-    <t>SMD-2, 3,8x1,8mm</t>
-  </si>
-  <si>
     <t>Knowles</t>
   </si>
   <si>
@@ -98,18 +98,18 @@
     <t>609-2450AT18B100E</t>
   </si>
   <si>
-    <t>C1, C2, C3, C4, C6, C7, C9, C13, C14, C15, C16, C17, C19, C21, C24, C29, C30, C31</t>
-  </si>
-  <si>
     <t>100n</t>
   </si>
   <si>
+    <t>C1, C2, C3, C6, C7, C13, C14, C15, C16, C17, C19, C21, C24, C29, C30, C31</t>
+  </si>
+  <si>
+    <t>0805</t>
+  </si>
+  <si>
     <t>Kondenzator, X7R, 10%, 50VDC</t>
   </si>
   <si>
-    <t>0805</t>
-  </si>
-  <si>
     <t>TAIYO YUDEN</t>
   </si>
   <si>
@@ -119,12 +119,12 @@
     <t>963-MCJCU21GBB7104KT</t>
   </si>
   <si>
+    <t>10n</t>
+  </si>
+  <si>
     <t>C5, C25</t>
   </si>
   <si>
-    <t>10n</t>
-  </si>
-  <si>
     <t>Kondenzator, C0G, 10%, 50VDC</t>
   </si>
   <si>
@@ -137,18 +137,18 @@
     <t>80-C0805C103K5RECAUT</t>
   </si>
   <si>
+    <t>22p</t>
+  </si>
+  <si>
     <t>C8, C28</t>
   </si>
   <si>
-    <t>22p</t>
+    <t>0402</t>
   </si>
   <si>
     <t>Kondenzator, C0G, 1%, 50VDC</t>
   </si>
   <si>
-    <t>0402</t>
-  </si>
-  <si>
     <t>KYOCERA AVX</t>
   </si>
   <si>
@@ -158,12 +158,12 @@
     <t>581-KAM05ACG1H220FH</t>
   </si>
   <si>
+    <t>15p</t>
+  </si>
+  <si>
     <t>C10, C11</t>
   </si>
   <si>
-    <t>15p</t>
-  </si>
-  <si>
     <t>Kondenzator, C0G, 10%, 160VDC</t>
   </si>
   <si>
@@ -173,30 +173,30 @@
     <t>581-08052U150J</t>
   </si>
   <si>
+    <t>10u/16V</t>
+  </si>
+  <si>
     <t>C12</t>
   </si>
   <si>
-    <t>10u/16V</t>
+    <t>1210</t>
   </si>
   <si>
     <t>Elektrolitski kondenzator, Ta, 10%, 16V</t>
   </si>
   <si>
-    <t>1210</t>
-  </si>
-  <si>
     <t>EEV106M035A9DAA</t>
   </si>
   <si>
     <t>80-EEV106M035A9DAA</t>
   </si>
   <si>
+    <t>4u7</t>
+  </si>
+  <si>
     <t>C18, C22</t>
   </si>
   <si>
-    <t>4u7</t>
-  </si>
-  <si>
     <t>TDK</t>
   </si>
   <si>
@@ -206,12 +206,12 @@
     <t>810-CGA4J1X7R1H475K1</t>
   </si>
   <si>
+    <t>100p</t>
+  </si>
+  <si>
     <t>C20</t>
   </si>
   <si>
-    <t>100p</t>
-  </si>
-  <si>
     <t>Kondenzator, C0G, 2%, 100VDC</t>
   </si>
   <si>
@@ -224,24 +224,24 @@
     <t>81-GCM1555C2A101GE2D</t>
   </si>
   <si>
+    <t>1p2</t>
+  </si>
+  <si>
     <t>C23</t>
   </si>
   <si>
-    <t>1p2</t>
-  </si>
-  <si>
     <t>QSCF500Q1R2B1GV001T</t>
   </si>
   <si>
     <t>609-QSCF500Q1R2B1GV0</t>
   </si>
   <si>
+    <t>1u</t>
+  </si>
+  <si>
     <t>C26, C27</t>
   </si>
   <si>
-    <t>1u</t>
-  </si>
-  <si>
     <t>0603</t>
   </si>
   <si>
@@ -251,12 +251,12 @@
     <t>810-C1608X7R1H105K08</t>
   </si>
   <si>
+    <t>Zelena</t>
+  </si>
+  <si>
     <t>D1, D2, D3</t>
   </si>
   <si>
-    <t>Zelena</t>
-  </si>
-  <si>
     <t>Dioda, svjetleća, 1,9V</t>
   </si>
   <si>
@@ -269,60 +269,60 @@
     <t>749-SM0805GCL</t>
   </si>
   <si>
+    <t>MPZ2012S601AT000</t>
+  </si>
+  <si>
     <t>FB1</t>
   </si>
   <si>
-    <t>MPZ2012S601AT000</t>
-  </si>
-  <si>
     <t>Feritna perla, 600Ohm</t>
   </si>
   <si>
     <t>810-MPZ2012S601AT000</t>
   </si>
   <si>
+    <t>MLPF-WB55-01E3</t>
+  </si>
+  <si>
     <t>IPD1</t>
   </si>
   <si>
-    <t>MLPF-WB55-01E3</t>
+    <t>SMD-6, 1,6x1 mm</t>
   </si>
   <si>
     <t>RF Filtar, 2.4-2.5GHz</t>
   </si>
   <si>
-    <t>SMD-6, 1,6x1 mm</t>
-  </si>
-  <si>
     <t>STMicroelectronics</t>
   </si>
   <si>
     <t>511-MLPF-WB55-01E3</t>
   </si>
   <si>
+    <t>USB4135-GF-A</t>
+  </si>
+  <si>
     <t>J1</t>
   </si>
   <si>
-    <t>USB4135-GF-A</t>
+    <t>SMD-10, 11,14x6,78mm</t>
   </si>
   <si>
     <t>USB-C priključak</t>
   </si>
   <si>
-    <t>SMD-10, 11,14x6,78mm</t>
-  </si>
-  <si>
     <t>Global Connector Technology</t>
   </si>
   <si>
     <t>640-USB4135-GF-A</t>
   </si>
   <si>
+    <t>10u</t>
+  </si>
+  <si>
     <t>L1</t>
   </si>
   <si>
-    <t>10u</t>
-  </si>
-  <si>
     <t>Zavojnica, neoklopljena, 500mADC,</t>
   </si>
   <si>
@@ -347,24 +347,24 @@
     <t>815-AIMC-0805-10NJT</t>
   </si>
   <si>
+    <t>3n3</t>
+  </si>
+  <si>
     <t>L3</t>
   </si>
   <si>
-    <t>3n3</t>
-  </si>
-  <si>
     <t>Zavojnica, neoklopljena, 400mADC</t>
   </si>
   <si>
     <t>609-L-07C3N3SV6T</t>
   </si>
   <si>
+    <t>2n7</t>
+  </si>
+  <si>
     <t>L4</t>
   </si>
   <si>
-    <t>2n7</t>
-  </si>
-  <si>
     <t>RF zavojnica, neoklopljena, 300mADC</t>
   </si>
   <si>
@@ -377,12 +377,12 @@
     <t>712-LRC0402CS2N7GV001TCT-ND</t>
   </si>
   <si>
+    <t>49R9</t>
+  </si>
+  <si>
     <t>R1, R3, R7, R9</t>
   </si>
   <si>
-    <t>49R9</t>
-  </si>
-  <si>
     <t>Otpornik, ±100ppm/C, 125mW</t>
   </si>
   <si>
@@ -392,12 +392,12 @@
     <t>603-AC0805FR-0749R9L</t>
   </si>
   <si>
+    <t>2k</t>
+  </si>
+  <si>
     <t>R2, R11</t>
   </si>
   <si>
-    <t>2k</t>
-  </si>
-  <si>
     <t>Otpornik, 1%, 125mW</t>
   </si>
   <si>
@@ -407,42 +407,42 @@
     <t>603-RC0805FR-102KL</t>
   </si>
   <si>
+    <t>4R7</t>
+  </si>
+  <si>
     <t>R4</t>
   </si>
   <si>
-    <t>4R7</t>
-  </si>
-  <si>
     <t>AC0805FR-074R7L</t>
   </si>
   <si>
     <t>603-AC0805FR-074R7L</t>
   </si>
   <si>
+    <t>52R3</t>
+  </si>
+  <si>
     <t>R5</t>
   </si>
   <si>
-    <t>52R3</t>
-  </si>
-  <si>
     <t>RC0805FR-0752R3L</t>
   </si>
   <si>
     <t>603-RC0805FR-0752R3L</t>
   </si>
   <si>
+    <t>0R0</t>
+  </si>
+  <si>
     <t>R6, R18, R19, R22</t>
   </si>
   <si>
-    <t>0R0</t>
+    <t>0402, 0603</t>
   </si>
   <si>
     <t>Otpornik, 1%, 100mW</t>
   </si>
   <si>
-    <t>0402, 0603</t>
-  </si>
-  <si>
     <t>Multicomp</t>
   </si>
   <si>
@@ -452,12 +452,12 @@
     <t>Farnell</t>
   </si>
   <si>
+    <t>10k</t>
+  </si>
+  <si>
     <t>R8</t>
   </si>
   <si>
-    <t>10k</t>
-  </si>
-  <si>
     <t>Otpornik, 5%, 125mW</t>
   </si>
   <si>
@@ -479,12 +479,12 @@
     <t>810-NTCG103JF103FT1</t>
   </si>
   <si>
+    <t>5k1</t>
+  </si>
+  <si>
     <t>R12, R14</t>
   </si>
   <si>
-    <t>5k1</t>
-  </si>
-  <si>
     <t>Otpornik, ±100ppm/C, 100mW</t>
   </si>
   <si>
@@ -494,12 +494,12 @@
     <t>603-AC0603FR-075K1L</t>
   </si>
   <si>
+    <t>1k5</t>
+  </si>
+  <si>
     <t>R13, R16, R20</t>
   </si>
   <si>
-    <t>1k5</t>
-  </si>
-  <si>
     <t>Otpornik, ±50ppm/C, 100mW</t>
   </si>
   <si>
@@ -512,12 +512,12 @@
     <t>594-MCU08050C1501FP5</t>
   </si>
   <si>
+    <t>2k2</t>
+  </si>
+  <si>
     <t>R15</t>
   </si>
   <si>
-    <t>2k2</t>
-  </si>
-  <si>
     <t>R17</t>
   </si>
   <si>
@@ -536,109 +536,115 @@
     <t>954-103AT-2</t>
   </si>
   <si>
+    <t>TL3301AF160QG</t>
+  </si>
+  <si>
     <t>S1</t>
   </si>
   <si>
-    <t>TL3301AF160QG</t>
+    <t>SMD-4, 6x6mm</t>
   </si>
   <si>
     <t>Taktilni prekidač</t>
   </si>
   <si>
-    <t>SMD-4, 6x6mm</t>
-  </si>
-  <si>
     <t>E-Switch</t>
   </si>
   <si>
     <t>612-TL3301AF1</t>
   </si>
   <si>
+    <t>BUF602</t>
+  </si>
+  <si>
     <t>U1</t>
   </si>
   <si>
-    <t>BUF602</t>
+    <t>SOIC-8</t>
   </si>
   <si>
     <t>Integrirani Buffer</t>
   </si>
   <si>
+    <t>Texas Instruments</t>
+  </si>
+  <si>
+    <t>BUF602ID</t>
+  </si>
+  <si>
+    <t>595-BUF602ID</t>
+  </si>
+  <si>
+    <t>AD8310ARMZ-REEL7</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>MSOP</t>
+  </si>
+  <si>
+    <t>Logaritamsko pojačalo</t>
+  </si>
+  <si>
+    <t>Analog Devices</t>
+  </si>
+  <si>
+    <t>584-AD8310ARMZ-R7</t>
+  </si>
+  <si>
+    <t>STM32WB55CGU6</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>UFQFPN-48</t>
+  </si>
+  <si>
+    <t>STM32 Mikrokontroler, 1,7-3,6V</t>
+  </si>
+  <si>
+    <t>511-STM32WB55CGU6</t>
+  </si>
+  <si>
+    <t>BQ24040DSQR</t>
+  </si>
+  <si>
+    <t>U4</t>
+  </si>
+  <si>
+    <t>WSON-10</t>
+  </si>
+  <si>
+    <t>Li-Ion baterija, 800mA</t>
+  </si>
+  <si>
+    <t>595-BQ24040DSQR</t>
+  </si>
+  <si>
+    <t>TPS73633DBVR</t>
+  </si>
+  <si>
+    <t>U5</t>
+  </si>
+  <si>
     <t>SOT-23</t>
   </si>
   <si>
-    <t>Texas Instruments</t>
-  </si>
-  <si>
-    <t>BUF602ID</t>
-  </si>
-  <si>
-    <t>595-BUF602ID</t>
-  </si>
-  <si>
-    <t>U2</t>
-  </si>
-  <si>
-    <t>AD8310ARMZ-REEL7</t>
-  </si>
-  <si>
-    <t>Logaritamsko pojačalo</t>
-  </si>
-  <si>
-    <t>MSOP</t>
-  </si>
-  <si>
-    <t>Analog Devices</t>
-  </si>
-  <si>
-    <t>584-AD8310ARMZ-R7</t>
-  </si>
-  <si>
-    <t>U3</t>
-  </si>
-  <si>
-    <t>STM32WB55CGU6</t>
-  </si>
-  <si>
-    <t>STM32 Mikrokontroler, 1,7-3,6V</t>
-  </si>
-  <si>
-    <t>UFQFPN-48</t>
-  </si>
-  <si>
-    <t>511-STM32WB55CGU6</t>
-  </si>
-  <si>
-    <t>U4</t>
-  </si>
-  <si>
-    <t>BQ24040DSQR</t>
-  </si>
-  <si>
-    <t>Li-Ion baterija, 800mA</t>
-  </si>
-  <si>
-    <t>WSON-10</t>
-  </si>
-  <si>
-    <t>595-BQ24040DSQR</t>
-  </si>
-  <si>
-    <t>U5</t>
-  </si>
-  <si>
-    <t>TPS73633DBVR</t>
-  </si>
-  <si>
     <t>IC Regulator, 3,3V, 400mADC</t>
   </si>
   <si>
     <t>595-TPS73633DBVR</t>
   </si>
   <si>
+    <t>74AHC1G17GWH</t>
+  </si>
+  <si>
     <t>U6</t>
   </si>
   <si>
-    <t>74AHC1G17GWH</t>
+    <t>SOT353-1</t>
   </si>
   <si>
     <t>Integrirani Schmittov okidni sklop</t>
@@ -650,18 +656,18 @@
     <t>771-74AHC1G17GWH</t>
   </si>
   <si>
+    <t>PROGRAMIRANJE</t>
+  </si>
+  <si>
     <t>X2</t>
   </si>
   <si>
-    <t>PROGRAMIRANJE MIKROKONTROLERA</t>
+    <t>SMD-10, 16x2,5mm</t>
   </si>
   <si>
     <t>Header 1x4</t>
   </si>
   <si>
-    <t>SMD-10, 16x2,5mm</t>
-  </si>
-  <si>
     <t>Amphenol Communications Solutions</t>
   </si>
   <si>
@@ -671,12 +677,12 @@
     <t>649-68001-204HLF</t>
   </si>
   <si>
+    <t>NX2016SA-32MHz</t>
+  </si>
+  <si>
     <t>Y1</t>
   </si>
   <si>
-    <t>NX2016SA-32MHz</t>
-  </si>
-  <si>
     <t>Kristalni oscilator 32KHz</t>
   </si>
   <si>
@@ -689,10 +695,10 @@
     <t>644-1375-1-ND</t>
   </si>
   <si>
+    <t>NX2012SA-32.768kHz</t>
+  </si>
+  <si>
     <t>Y2</t>
-  </si>
-  <si>
-    <t>NX2012SA-32.768kHz</t>
   </si>
   <si>
     <t>Kristalni oscilator, 32.768KHz</t>
@@ -717,7 +723,6 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <charset val="238"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1101,24 +1106,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BA178F5-4193-452D-A01B-CC63F7C17B61}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A4D3B91-B641-4A87-AEBF-55FFECF58180}">
   <dimension ref="A1:K41"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" customWidth="1"/>
-    <col min="2" max="2" width="20.88671875" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="6" max="6" width="26.44140625" customWidth="1"/>
-    <col min="7" max="7" width="18.5546875" customWidth="1"/>
-    <col min="8" max="8" width="22.33203125" customWidth="1"/>
-    <col min="9" max="9" width="20.109375" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="19.33203125" customWidth="1"/>
+    <col min="1" max="1" width="21.5703125" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" customWidth="1"/>
+    <col min="6" max="6" width="27.42578125" customWidth="1"/>
+    <col min="7" max="7" width="19.140625" customWidth="1"/>
+    <col min="8" max="8" width="23.140625" customWidth="1"/>
+    <col min="9" max="9" width="20.85546875" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1153,7 +1158,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -1170,7 +1175,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>16</v>
@@ -1188,7 +1193,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
@@ -1215,11 +1220,11 @@
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>25</v>
       </c>
@@ -1227,10 +1232,10 @@
         <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>28</v>
@@ -1245,16 +1250,16 @@
         <v>30</v>
       </c>
       <c r="I4" s="1">
-        <v>0.21437</v>
+        <v>0.21510000000000001</v>
       </c>
       <c r="J4" s="1">
         <v>2</v>
       </c>
       <c r="K4" s="1">
-        <v>0.42874000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.43020000000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>31</v>
       </c>
@@ -1280,16 +1285,16 @@
         <v>37</v>
       </c>
       <c r="I5" s="1">
-        <v>0.27439999999999998</v>
+        <v>0.27533000000000002</v>
       </c>
       <c r="J5" s="1">
         <v>2</v>
       </c>
       <c r="K5" s="1">
-        <v>0.54879</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.55066000000000004</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>38</v>
       </c>
@@ -1297,10 +1302,10 @@
         <v>39</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>35</v>
@@ -1315,16 +1320,16 @@
         <v>42</v>
       </c>
       <c r="I6" s="1">
-        <v>0.30012</v>
+        <v>0.30114000000000002</v>
       </c>
       <c r="J6" s="1">
         <v>2</v>
       </c>
       <c r="K6" s="1">
-        <v>0.60024</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.60228000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>43</v>
       </c>
@@ -1350,16 +1355,16 @@
         <v>48</v>
       </c>
       <c r="I7" s="1">
-        <v>0.28297</v>
+        <v>0.28393000000000002</v>
       </c>
       <c r="J7" s="1">
         <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>0.28297</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.28393000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>49</v>
       </c>
@@ -1367,10 +1372,10 @@
         <v>50</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>51</v>
@@ -1385,16 +1390,16 @@
         <v>53</v>
       </c>
       <c r="I8" s="1">
-        <v>0.48019000000000001</v>
+        <v>0.48182000000000003</v>
       </c>
       <c r="J8" s="1">
         <v>2</v>
       </c>
       <c r="K8" s="1">
-        <v>0.96038999999999997</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.96365000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>54</v>
       </c>
@@ -1402,10 +1407,10 @@
         <v>55</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>57</v>
@@ -1420,16 +1425,16 @@
         <v>59</v>
       </c>
       <c r="I9" s="1">
-        <v>0.10290000000000001</v>
+        <v>0.10324999999999999</v>
       </c>
       <c r="J9" s="1">
         <v>1</v>
       </c>
       <c r="K9" s="1">
-        <v>0.10290000000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.10324999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>60</v>
       </c>
@@ -1437,10 +1442,10 @@
         <v>61</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>15</v>
@@ -1455,16 +1460,16 @@
         <v>63</v>
       </c>
       <c r="I10" s="1">
-        <v>0.13719999999999999</v>
+        <v>0.13766</v>
       </c>
       <c r="J10" s="1">
         <v>1</v>
       </c>
       <c r="K10" s="1">
-        <v>0.13719999999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.13766</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>64</v>
       </c>
@@ -1472,10 +1477,10 @@
         <v>65</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>51</v>
@@ -1490,16 +1495,16 @@
         <v>68</v>
       </c>
       <c r="I11" s="1">
-        <v>0.18865000000000001</v>
+        <v>0.18929000000000001</v>
       </c>
       <c r="J11" s="1">
         <v>2</v>
       </c>
       <c r="K11" s="1">
-        <v>0.37730000000000002</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.37858000000000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>69</v>
       </c>
@@ -1507,10 +1512,10 @@
         <v>70</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>72</v>
@@ -1530,7 +1535,7 @@
       </c>
       <c r="K12" s="1"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>75</v>
       </c>
@@ -1538,16 +1543,16 @@
         <v>76</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>51</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>16</v>
@@ -1556,16 +1561,16 @@
         <v>78</v>
       </c>
       <c r="I13" s="1">
-        <v>9.4320000000000001E-2</v>
+        <v>9.4640000000000002E-2</v>
       </c>
       <c r="J13" s="1">
         <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>9.4320000000000001E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+        <v>9.4640000000000002E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>79</v>
       </c>
@@ -1582,7 +1587,7 @@
         <v>83</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>16</v>
@@ -1591,16 +1596,16 @@
         <v>84</v>
       </c>
       <c r="I14" s="1">
-        <v>0.31727</v>
+        <v>0.31835000000000002</v>
       </c>
       <c r="J14" s="1">
         <v>1</v>
       </c>
       <c r="K14" s="1">
-        <v>0.31727</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.31835000000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>85</v>
       </c>
@@ -1617,7 +1622,7 @@
         <v>89</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>16</v>
@@ -1626,16 +1631,16 @@
         <v>90</v>
       </c>
       <c r="I15" s="1">
-        <v>0.58309</v>
+        <v>0.58506999999999998</v>
       </c>
       <c r="J15" s="1">
         <v>1</v>
       </c>
       <c r="K15" s="1">
-        <v>0.58309</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.58506999999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>91</v>
       </c>
@@ -1643,10 +1648,10 @@
         <v>92</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>22</v>
@@ -1661,27 +1666,27 @@
         <v>95</v>
       </c>
       <c r="I16" s="1">
-        <v>9.4320000000000001E-2</v>
+        <v>0.10324999999999999</v>
       </c>
       <c r="J16" s="1">
         <v>1</v>
       </c>
       <c r="K16" s="1">
-        <v>9.4320000000000001E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.10324999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="C17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>98</v>
@@ -1696,16 +1701,16 @@
         <v>100</v>
       </c>
       <c r="I17" s="1">
-        <v>0.10290000000000001</v>
+        <v>0.11185</v>
       </c>
       <c r="J17" s="1">
         <v>1</v>
       </c>
       <c r="K17" s="1">
-        <v>0.10290000000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.11185</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>101</v>
       </c>
@@ -1713,10 +1718,10 @@
         <v>102</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
@@ -1732,7 +1737,7 @@
       </c>
       <c r="K18" s="1"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>105</v>
       </c>
@@ -1740,10 +1745,10 @@
         <v>106</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>15</v>
@@ -1758,16 +1763,16 @@
         <v>110</v>
       </c>
       <c r="I19" s="1">
-        <v>8.5750000000000007E-2</v>
+        <v>8.6040000000000005E-2</v>
       </c>
       <c r="J19" s="1">
         <v>1</v>
       </c>
       <c r="K19" s="1">
-        <v>8.5750000000000007E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+        <v>8.6040000000000005E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>111</v>
       </c>
@@ -1775,10 +1780,10 @@
         <v>112</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>28</v>
@@ -1793,16 +1798,16 @@
         <v>115</v>
       </c>
       <c r="I20" s="1">
-        <v>1.0290000000000001E-2</v>
+        <v>1.0319999999999999E-2</v>
       </c>
       <c r="J20" s="1">
         <v>4</v>
       </c>
       <c r="K20" s="1">
-        <v>0.10290000000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.10324999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>116</v>
       </c>
@@ -1810,10 +1815,10 @@
         <v>117</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>28</v>
@@ -1828,16 +1833,16 @@
         <v>120</v>
       </c>
       <c r="I21" s="1">
-        <v>1.6289999999999999E-2</v>
+        <v>1.635E-2</v>
       </c>
       <c r="J21" s="1">
         <v>2</v>
       </c>
       <c r="K21" s="1">
-        <v>0.16292000000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.16347999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>121</v>
       </c>
@@ -1845,10 +1850,10 @@
         <v>122</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>28</v>
@@ -1863,16 +1868,16 @@
         <v>124</v>
       </c>
       <c r="I22" s="1">
-        <v>8.5750000000000007E-2</v>
+        <v>8.6040000000000005E-2</v>
       </c>
       <c r="J22" s="1">
         <v>1</v>
       </c>
       <c r="K22" s="1">
-        <v>8.5750000000000007E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+        <v>8.6040000000000005E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>125</v>
       </c>
@@ -1880,10 +1885,10 @@
         <v>126</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>28</v>
@@ -1898,16 +1903,16 @@
         <v>128</v>
       </c>
       <c r="I23" s="1">
-        <v>8.5750000000000007E-2</v>
+        <v>8.6040000000000005E-2</v>
       </c>
       <c r="J23" s="1">
         <v>1</v>
       </c>
       <c r="K23" s="1">
-        <v>8.5750000000000007E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+        <v>8.6040000000000005E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>129</v>
       </c>
@@ -1933,16 +1938,16 @@
         <v>134</v>
       </c>
       <c r="I24" s="1">
-        <v>4.0200000000000001E-3</v>
+        <v>4.0099999999999997E-3</v>
       </c>
       <c r="J24" s="1">
         <v>4</v>
       </c>
       <c r="K24" s="1">
-        <v>40.19</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+        <v>40.14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>136</v>
       </c>
@@ -1950,10 +1955,10 @@
         <v>137</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>28</v>
@@ -1968,27 +1973,27 @@
         <v>140</v>
       </c>
       <c r="I25" s="1">
-        <v>0.18865000000000001</v>
+        <v>0.18929000000000001</v>
       </c>
       <c r="J25" s="1">
         <v>1</v>
       </c>
       <c r="K25" s="1">
-        <v>0.18865000000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.18929000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="C26" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>51</v>
@@ -2003,16 +2008,16 @@
         <v>144</v>
       </c>
       <c r="I26" s="1">
-        <v>8.5750000000000007E-2</v>
+        <v>8.6040000000000005E-2</v>
       </c>
       <c r="J26" s="1">
         <v>1</v>
       </c>
       <c r="K26" s="1">
-        <v>8.5750000000000007E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+        <v>8.6040000000000005E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>145</v>
       </c>
@@ -2020,10 +2025,10 @@
         <v>146</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>28</v>
@@ -2038,16 +2043,16 @@
         <v>149</v>
       </c>
       <c r="I27" s="1">
-        <v>1.0290000000000001E-2</v>
+        <v>1.0319999999999999E-2</v>
       </c>
       <c r="J27" s="1">
         <v>2</v>
       </c>
       <c r="K27" s="1">
-        <v>0.10290000000000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.10324999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>150</v>
       </c>
@@ -2055,10 +2060,10 @@
         <v>151</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>153</v>
@@ -2073,16 +2078,16 @@
         <v>155</v>
       </c>
       <c r="I28" s="1">
-        <v>7.3529999999999998E-2</v>
+        <v>7.4029999999999999E-2</v>
       </c>
       <c r="J28" s="1">
         <v>3</v>
       </c>
       <c r="K28" s="1">
-        <v>0.22059000000000001</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.22209000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>156</v>
       </c>
@@ -2090,10 +2095,10 @@
         <v>157</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>153</v>
@@ -2108,27 +2113,27 @@
         <v>155</v>
       </c>
       <c r="I29" s="1">
-        <v>7.3529999999999998E-2</v>
+        <v>7.4029999999999999E-2</v>
       </c>
       <c r="J29" s="1">
         <v>1</v>
       </c>
       <c r="K29" s="1">
-        <v>7.3529999999999998E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+        <v>7.4029999999999999E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="C30" s="2" t="s">
-        <v>131</v>
+        <v>66</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>133</v>
@@ -2143,27 +2148,27 @@
         <v>134</v>
       </c>
       <c r="I30" s="1">
-        <v>4.0200000000000001E-3</v>
+        <v>4.0099999999999997E-3</v>
       </c>
       <c r="J30" s="1">
         <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>40.19</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+        <v>40.14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="C31" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>161</v>
@@ -2187,7 +2192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>164</v>
       </c>
@@ -2204,7 +2209,7 @@
         <v>168</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>16</v>
@@ -2213,16 +2218,16 @@
         <v>169</v>
       </c>
       <c r="I32" s="1">
-        <v>0.29154999999999998</v>
+        <v>0.29254000000000002</v>
       </c>
       <c r="J32" s="1">
         <v>1</v>
       </c>
       <c r="K32" s="1">
-        <v>0.29154999999999998</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.29254000000000002</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>170</v>
       </c>
@@ -2248,16 +2253,16 @@
         <v>176</v>
       </c>
       <c r="I33" s="1">
-        <v>5.81</v>
+        <v>5.82</v>
       </c>
       <c r="J33" s="1">
         <v>1</v>
       </c>
       <c r="K33" s="1">
-        <v>5.81</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+        <v>5.82</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>177</v>
       </c>
@@ -2274,7 +2279,7 @@
         <v>181</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>16</v>
@@ -2283,16 +2288,16 @@
         <v>182</v>
       </c>
       <c r="I34" s="1">
-        <v>12.3</v>
+        <v>12.34</v>
       </c>
       <c r="J34" s="1">
         <v>1</v>
       </c>
       <c r="K34" s="1">
-        <v>12.3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+        <v>12.34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>183</v>
       </c>
@@ -2309,7 +2314,7 @@
         <v>83</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>16</v>
@@ -2318,16 +2323,16 @@
         <v>187</v>
       </c>
       <c r="I35" s="1">
-        <v>7.03</v>
+        <v>7.06</v>
       </c>
       <c r="J35" s="1">
         <v>1</v>
       </c>
       <c r="K35" s="1">
-        <v>7.03</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+        <v>7.06</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>188</v>
       </c>
@@ -2344,7 +2349,7 @@
         <v>174</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>16</v>
@@ -2353,16 +2358,16 @@
         <v>192</v>
       </c>
       <c r="I36" s="1">
-        <v>0.78888999999999998</v>
+        <v>0.79157</v>
       </c>
       <c r="J36" s="1">
         <v>1</v>
       </c>
       <c r="K36" s="1">
-        <v>0.78888999999999998</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.79157</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>193</v>
       </c>
@@ -2373,45 +2378,45 @@
         <v>195</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>174</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I37" s="1">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="J37" s="1">
         <v>1</v>
       </c>
       <c r="K37" s="1">
-        <v>2.15</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>21</v>
+        <v>201</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>198</v>
@@ -2420,77 +2425,77 @@
         <v>16</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I38" s="1">
-        <v>0.11147</v>
+        <v>0.10324999999999999</v>
       </c>
       <c r="J38" s="1">
         <v>1</v>
       </c>
       <c r="K38" s="1">
-        <v>0.11147</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.10324999999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I39" s="1">
-        <v>0.34300000000000003</v>
+        <v>0.34416000000000002</v>
       </c>
       <c r="J39" s="1">
         <v>1</v>
       </c>
       <c r="K39" s="1">
-        <v>0.34300000000000003</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.34416000000000002</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>211</v>
+        <v>20</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>21</v>
+        <v>213</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>109</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="I40" s="1"/>
       <c r="J40" s="1">
@@ -2498,39 +2503,39 @@
       </c>
       <c r="K40" s="1"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>217</v>
+        <v>20</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>21</v>
+        <v>219</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="I41" s="1">
-        <v>0.72887000000000002</v>
+        <v>0.73133999999999999</v>
       </c>
       <c r="J41" s="1">
         <v>1</v>
       </c>
       <c r="K41" s="1">
-        <v>0.72887000000000002</v>
+        <v>0.73133999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/IBC_prijamnik_VB/Project Outputs for IBC_prijamnik_VB/IBC_prijamnik_VB.xlsx
+++ b/IBC_prijamnik_VB/Project Outputs for IBC_prijamnik_VB/IBC_prijamnik_VB.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FER\3. godina\6. sem\zavrsni\IBC_prijamnik_VB\Project Outputs for IBC_prijamnik_VB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{989124C7-2494-4156-B398-2F0F01D2CB12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1019ED1F-336B-4FE6-8A45-7C595A758E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{5636603A-DEFA-48BC-8903-7E90C53F8C7C}"/>
   </bookViews>
@@ -590,9 +590,6 @@
     <t>WSON-10</t>
   </si>
   <si>
-    <t>Li-Ion baterija, 800mA</t>
-  </si>
-  <si>
     <t>595-BQ24040DSQR</t>
   </si>
   <si>
@@ -714,6 +711,9 @@
   </si>
   <si>
     <t xml:space="preserve">Zelena </t>
+  </si>
+  <si>
+    <t>Li-Ion akumulator, 800mA</t>
   </si>
 </sst>
 </file>
@@ -1144,7 +1144,7 @@
   <sheetData>
     <row r="1" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -1153,28 +1153,28 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="H1" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>217</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>218</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>4</v>
@@ -1308,7 +1308,7 @@
         <v>181</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>182</v>
+        <v>223</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>165</v>
@@ -1320,7 +1320,7 @@
         <v>10</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J5" s="1">
         <v>0.79157</v>
@@ -1337,28 +1337,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>165</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J6" s="1">
         <v>2.16</v>
@@ -1375,28 +1375,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>194</v>
       </c>
       <c r="J7" s="1">
         <v>0.10324999999999999</v>
@@ -1489,28 +1489,28 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>202</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="H10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>205</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>206</v>
       </c>
       <c r="J10" s="1">
         <v>0.499</v>
@@ -1527,28 +1527,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>208</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="H11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>212</v>
       </c>
       <c r="J11" s="1">
         <v>0.73133999999999999</v>
@@ -1603,7 +1603,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>63</v>
@@ -2073,10 +2073,10 @@
         <v>96</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>10</v>
@@ -2631,28 +2631,28 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C40" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="E40" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="F40" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="F40" s="2" t="s">
+      <c r="G40" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="G40" s="2" t="s">
+      <c r="H40" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I40" s="2" t="s">
         <v>199</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="J40" s="1">
         <v>0.34416000000000002</v>
